--- a/data_lake/bart_temp_med/dt=2026-07-17/temperaturamed.xlsx
+++ b/data_lake/bart_temp_med/dt=2026-07-17/temperaturamed.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Mi unidad\OSPA\01. Tematicas\05. Datos Hidrometeorologicos\01. Productos\02.Tablas\temporales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE7D9CE8-CFD7-4EAA-9EC5-A156F8866631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BED53A1-596B-4CCD-AF60-D2E458BF613F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="729" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,6 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DHIME!$A$1:$S$159</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Temperatura!$Y$1:$Y$210</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Temperatura!$B$4:$R$29</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -6348,8 +6347,8 @@
     <col min="43" max="43" width="20.7109375" style="53" customWidth="1"/>
     <col min="44" max="44" width="24.85546875" style="69" customWidth="1"/>
     <col min="45" max="45" width="13.28515625" style="70" bestFit="1" customWidth="1"/>
-    <col min="46" max="102" width="32.42578125" style="50" customWidth="1"/>
-    <col min="103" max="16384" width="32.42578125" style="50"/>
+    <col min="46" max="103" width="32.42578125" style="50" customWidth="1"/>
+    <col min="104" max="16384" width="32.42578125" style="50"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" x14ac:dyDescent="0.2">
@@ -6677,7 +6676,9 @@
       <c r="Y5" s="56">
         <v>28.4</v>
       </c>
-      <c r="Z5" s="56"/>
+      <c r="Z5" s="56">
+        <v>28.9</v>
+      </c>
       <c r="AA5" s="56"/>
       <c r="AB5" s="56"/>
       <c r="AC5" s="56"/>
@@ -6695,11 +6696,11 @@
       <c r="AO5" s="56"/>
       <c r="AP5" s="58">
         <f t="shared" ref="AP5:AP68" si="0">COUNTIF(K5:AO5,"&gt;0")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ5" s="71">
         <f t="shared" ref="AQ5:AQ68" si="1">IF(AP5&gt;14,AVERAGE(K5:AO5),"")</f>
-        <v>28.866666666666671</v>
+        <v>28.868750000000002</v>
       </c>
       <c r="AR5" s="71">
         <f>IFERROR(VLOOKUP(A5,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -6707,7 +6708,7 @@
       </c>
       <c r="AS5" s="71">
         <f t="shared" ref="AS5:AS68" si="2">IF(OR(AQ5="",AR5=""),"",IFERROR(AQ5-AR5,""))</f>
-        <v>0.71345177769540058</v>
+        <v>0.71553511102873202</v>
       </c>
     </row>
     <row r="6" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6786,7 +6787,9 @@
       <c r="Y6" s="56">
         <v>28.7</v>
       </c>
-      <c r="Z6" s="56"/>
+      <c r="Z6" s="56">
+        <v>29.5</v>
+      </c>
       <c r="AA6" s="56"/>
       <c r="AB6" s="56"/>
       <c r="AC6" s="56"/>
@@ -6804,11 +6807,11 @@
       <c r="AO6" s="56"/>
       <c r="AP6" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ6" s="71">
         <f t="shared" si="1"/>
-        <v>28.873333333333331</v>
+        <v>28.912499999999998</v>
       </c>
       <c r="AR6" s="71">
         <f>IFERROR(VLOOKUP(A6,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -6816,7 +6819,7 @@
       </c>
       <c r="AS6" s="71">
         <f t="shared" si="2"/>
-        <v>0.47809944438451168</v>
+        <v>0.51726611105117826</v>
       </c>
     </row>
     <row r="7" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6895,7 +6898,9 @@
       <c r="Y7" s="56">
         <v>33.1</v>
       </c>
-      <c r="Z7" s="56"/>
+      <c r="Z7" s="56">
+        <v>33.4</v>
+      </c>
       <c r="AA7" s="56"/>
       <c r="AB7" s="56"/>
       <c r="AC7" s="56"/>
@@ -6913,11 +6918,11 @@
       <c r="AO7" s="56"/>
       <c r="AP7" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ7" s="71">
         <f t="shared" si="1"/>
-        <v>31.846666666666671</v>
+        <v>31.943750000000001</v>
       </c>
       <c r="AR7" s="71">
         <f>IFERROR(VLOOKUP(A7,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -6925,7 +6930,7 @@
       </c>
       <c r="AS7" s="71">
         <f t="shared" si="2"/>
-        <v>2.6464861751152107</v>
+        <v>2.743569508448541</v>
       </c>
     </row>
     <row r="8" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7004,7 +7009,9 @@
       <c r="Y8" s="56">
         <v>30.7</v>
       </c>
-      <c r="Z8" s="56"/>
+      <c r="Z8" s="56">
+        <v>30.4</v>
+      </c>
       <c r="AA8" s="56"/>
       <c r="AB8" s="56"/>
       <c r="AC8" s="56"/>
@@ -7022,11 +7029,11 @@
       <c r="AO8" s="56"/>
       <c r="AP8" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ8" s="71">
         <f t="shared" si="1"/>
-        <v>29.966666666666661</v>
+        <v>29.993749999999995</v>
       </c>
       <c r="AR8" s="71">
         <f>IFERROR(VLOOKUP(A8,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7034,7 +7041,7 @@
       </c>
       <c r="AS8" s="71">
         <f t="shared" si="2"/>
-        <v>1.3881273504952603</v>
+        <v>1.4152106838285938</v>
       </c>
     </row>
     <row r="9" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7113,7 +7120,9 @@
       <c r="Y9" s="56">
         <v>30.5</v>
       </c>
-      <c r="Z9" s="56"/>
+      <c r="Z9" s="56">
+        <v>30</v>
+      </c>
       <c r="AA9" s="56"/>
       <c r="AB9" s="56"/>
       <c r="AC9" s="56"/>
@@ -7131,11 +7140,11 @@
       <c r="AO9" s="56"/>
       <c r="AP9" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ9" s="71">
         <f t="shared" si="1"/>
-        <v>29.65333333333334</v>
+        <v>29.675000000000004</v>
       </c>
       <c r="AR9" s="71">
         <f>IFERROR(VLOOKUP(A9,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7143,7 +7152,7 @@
       </c>
       <c r="AS9" s="71">
         <f t="shared" si="2"/>
-        <v>-0.13413564929689059</v>
+        <v>-0.11246898263022587</v>
       </c>
     </row>
     <row r="10" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7222,7 +7231,9 @@
       <c r="Y10" s="56">
         <v>33</v>
       </c>
-      <c r="Z10" s="56"/>
+      <c r="Z10" s="56">
+        <v>32.200000000000003</v>
+      </c>
       <c r="AA10" s="56"/>
       <c r="AB10" s="56"/>
       <c r="AC10" s="56"/>
@@ -7240,11 +7251,11 @@
       <c r="AO10" s="56"/>
       <c r="AP10" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ10" s="71">
         <f t="shared" si="1"/>
-        <v>31.793333333333337</v>
+        <v>31.818750000000001</v>
       </c>
       <c r="AR10" s="71">
         <f>IFERROR(VLOOKUP(A10,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7252,7 +7263,7 @@
       </c>
       <c r="AS10" s="71">
         <f t="shared" si="2"/>
-        <v>1.7139112989282772</v>
+        <v>1.7393279655949421</v>
       </c>
     </row>
     <row r="11" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7331,7 +7342,9 @@
       <c r="Y11" s="56">
         <v>34.4</v>
       </c>
-      <c r="Z11" s="56"/>
+      <c r="Z11" s="56">
+        <v>33.799999999999997</v>
+      </c>
       <c r="AA11" s="56"/>
       <c r="AB11" s="56"/>
       <c r="AC11" s="56"/>
@@ -7349,11 +7362,11 @@
       <c r="AO11" s="56"/>
       <c r="AP11" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ11" s="71">
         <f t="shared" si="1"/>
-        <v>33.053333333333327</v>
+        <v>33.099999999999994</v>
       </c>
       <c r="AR11" s="71">
         <f>IFERROR(VLOOKUP(A11,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7361,7 +7374,7 @@
       </c>
       <c r="AS11" s="71">
         <f t="shared" si="2"/>
-        <v>3.0494192561054767</v>
+        <v>3.0960859227721436</v>
       </c>
     </row>
     <row r="12" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7440,7 +7453,9 @@
       <c r="Y12" s="56">
         <v>31.5</v>
       </c>
-      <c r="Z12" s="56"/>
+      <c r="Z12" s="56">
+        <v>32</v>
+      </c>
       <c r="AA12" s="56"/>
       <c r="AB12" s="56"/>
       <c r="AC12" s="56"/>
@@ -7458,11 +7473,11 @@
       <c r="AO12" s="56"/>
       <c r="AP12" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ12" s="71">
         <f t="shared" si="1"/>
-        <v>30.319999999999997</v>
+        <v>30.424999999999997</v>
       </c>
       <c r="AR12" s="71">
         <f>IFERROR(VLOOKUP(A12,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7470,7 +7485,7 @@
       </c>
       <c r="AS12" s="71">
         <f t="shared" si="2"/>
-        <v>2.0543336106844166</v>
+        <v>2.159333610684417</v>
       </c>
     </row>
     <row r="13" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7549,7 +7564,9 @@
       <c r="Y13" s="56">
         <v>31.7</v>
       </c>
-      <c r="Z13" s="56"/>
+      <c r="Z13" s="56">
+        <v>32.9</v>
+      </c>
       <c r="AA13" s="56"/>
       <c r="AB13" s="56"/>
       <c r="AC13" s="56"/>
@@ -7567,11 +7584,11 @@
       <c r="AO13" s="56"/>
       <c r="AP13" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ13" s="71">
         <f t="shared" si="1"/>
-        <v>30.046666666666667</v>
+        <v>30.224999999999998</v>
       </c>
       <c r="AR13" s="71">
         <f>IFERROR(VLOOKUP(A13,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7579,7 +7596,7 @@
       </c>
       <c r="AS13" s="71">
         <f t="shared" si="2"/>
-        <v>1.7172719688543054</v>
+        <v>1.8956053021876365</v>
       </c>
     </row>
     <row r="14" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7658,7 +7675,9 @@
       <c r="Y14" s="56">
         <v>25.4</v>
       </c>
-      <c r="Z14" s="56"/>
+      <c r="Z14" s="56">
+        <v>26.2</v>
+      </c>
       <c r="AA14" s="56"/>
       <c r="AB14" s="56"/>
       <c r="AC14" s="56"/>
@@ -7676,11 +7695,11 @@
       <c r="AO14" s="56"/>
       <c r="AP14" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ14" s="71">
         <f t="shared" si="1"/>
-        <v>23.74</v>
+        <v>23.893749999999997</v>
       </c>
       <c r="AR14" s="71">
         <f>IFERROR(VLOOKUP(A14,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7688,7 +7707,7 @@
       </c>
       <c r="AS14" s="71">
         <f t="shared" si="2"/>
-        <v>2.0184599761051487</v>
+        <v>2.1722099761051474</v>
       </c>
     </row>
     <row r="15" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7767,7 +7786,9 @@
       <c r="Y15" s="56">
         <v>31.2</v>
       </c>
-      <c r="Z15" s="56"/>
+      <c r="Z15" s="56">
+        <v>30.1</v>
+      </c>
       <c r="AA15" s="56"/>
       <c r="AB15" s="56"/>
       <c r="AC15" s="56"/>
@@ -7785,11 +7806,11 @@
       <c r="AO15" s="56"/>
       <c r="AP15" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ15" s="71">
         <f t="shared" si="1"/>
-        <v>29.119999999999997</v>
+        <v>29.181249999999999</v>
       </c>
       <c r="AR15" s="71">
         <f>IFERROR(VLOOKUP(A15,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7797,7 +7818,7 @@
       </c>
       <c r="AS15" s="71">
         <f t="shared" si="2"/>
-        <v>0.88449462365591813</v>
+        <v>0.94574462365591927</v>
       </c>
     </row>
     <row r="16" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7876,7 +7897,9 @@
       <c r="Y16" s="56">
         <v>30.5</v>
       </c>
-      <c r="Z16" s="56"/>
+      <c r="Z16" s="56">
+        <v>30.4</v>
+      </c>
       <c r="AA16" s="56"/>
       <c r="AB16" s="56"/>
       <c r="AC16" s="56"/>
@@ -7894,11 +7917,11 @@
       <c r="AO16" s="56"/>
       <c r="AP16" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ16" s="71">
         <f t="shared" si="1"/>
-        <v>28.486666666666668</v>
+        <v>28.606249999999999</v>
       </c>
       <c r="AR16" s="71">
         <f>IFERROR(VLOOKUP(A16,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7906,7 +7929,7 @@
       </c>
       <c r="AS16" s="71">
         <f t="shared" si="2"/>
-        <v>0.84901381826368905</v>
+        <v>0.9685971515970202</v>
       </c>
     </row>
     <row r="17" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7985,7 +8008,9 @@
       <c r="Y17" s="56">
         <v>25.2</v>
       </c>
-      <c r="Z17" s="56"/>
+      <c r="Z17" s="56">
+        <v>26.3</v>
+      </c>
       <c r="AA17" s="56"/>
       <c r="AB17" s="56"/>
       <c r="AC17" s="56"/>
@@ -8003,11 +8028,11 @@
       <c r="AO17" s="56"/>
       <c r="AP17" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ17" s="71">
         <f t="shared" si="1"/>
-        <v>24.753333333333337</v>
+        <v>24.850000000000005</v>
       </c>
       <c r="AR17" s="71">
         <f>IFERROR(VLOOKUP(A17,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8015,7 +8040,7 @@
       </c>
       <c r="AS17" s="71">
         <f t="shared" si="2"/>
-        <v>0.76970966417713882</v>
+        <v>0.86637633084380639</v>
       </c>
     </row>
     <row r="18" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8094,7 +8119,9 @@
       <c r="Y18" s="56">
         <v>18.2</v>
       </c>
-      <c r="Z18" s="56"/>
+      <c r="Z18" s="56">
+        <v>19.100000000000001</v>
+      </c>
       <c r="AA18" s="56"/>
       <c r="AB18" s="56"/>
       <c r="AC18" s="56"/>
@@ -8112,11 +8139,11 @@
       <c r="AO18" s="56"/>
       <c r="AP18" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ18" s="71">
         <f t="shared" si="1"/>
-        <v>18.82</v>
+        <v>18.837500000000002</v>
       </c>
       <c r="AR18" s="71">
         <f>IFERROR(VLOOKUP(A18,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8124,7 +8151,7 @@
       </c>
       <c r="AS18" s="71">
         <f t="shared" si="2"/>
-        <v>1.4016487455197186</v>
+        <v>1.4191487455197205</v>
       </c>
     </row>
     <row r="19" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8203,7 +8230,9 @@
       <c r="Y19" s="56">
         <v>26.4</v>
       </c>
-      <c r="Z19" s="56"/>
+      <c r="Z19" s="56">
+        <v>26</v>
+      </c>
       <c r="AA19" s="56"/>
       <c r="AB19" s="56"/>
       <c r="AC19" s="56"/>
@@ -8221,11 +8250,11 @@
       <c r="AO19" s="56"/>
       <c r="AP19" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ19" s="71">
         <f t="shared" si="1"/>
-        <v>24.613333333333333</v>
+        <v>24.7</v>
       </c>
       <c r="AR19" s="71">
         <f>IFERROR(VLOOKUP(A19,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8233,7 +8262,7 @@
       </c>
       <c r="AS19" s="71">
         <f t="shared" si="2"/>
-        <v>2.4797983870967819</v>
+        <v>2.5664650537634479</v>
       </c>
     </row>
     <row r="20" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8312,7 +8341,9 @@
       <c r="Y20" s="56">
         <v>26</v>
       </c>
-      <c r="Z20" s="56"/>
+      <c r="Z20" s="56">
+        <v>25.2</v>
+      </c>
       <c r="AA20" s="56"/>
       <c r="AB20" s="56"/>
       <c r="AC20" s="56"/>
@@ -8330,11 +8361,11 @@
       <c r="AO20" s="56"/>
       <c r="AP20" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ20" s="71">
         <f t="shared" si="1"/>
-        <v>24.880000000000003</v>
+        <v>24.900000000000002</v>
       </c>
       <c r="AR20" s="71">
         <f>IFERROR(VLOOKUP(A20,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8342,7 +8373,7 @@
       </c>
       <c r="AS20" s="71">
         <f t="shared" si="2"/>
-        <v>2.2723345740281324</v>
+        <v>2.292334574028132</v>
       </c>
     </row>
     <row r="21" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8421,7 +8452,9 @@
       <c r="Y21" s="56">
         <v>29.4</v>
       </c>
-      <c r="Z21" s="56"/>
+      <c r="Z21" s="56">
+        <v>27.8</v>
+      </c>
       <c r="AA21" s="56"/>
       <c r="AB21" s="56"/>
       <c r="AC21" s="56"/>
@@ -8439,11 +8472,11 @@
       <c r="AO21" s="56"/>
       <c r="AP21" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ21" s="71">
         <f t="shared" si="1"/>
-        <v>27.126666666666665</v>
+        <v>27.168749999999999</v>
       </c>
       <c r="AR21" s="71">
         <f>IFERROR(VLOOKUP(A21,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8451,7 +8484,7 @@
       </c>
       <c r="AS21" s="71">
         <f t="shared" si="2"/>
-        <v>2.4365847749095337</v>
+        <v>2.4786681082428679</v>
       </c>
     </row>
     <row r="22" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8530,7 +8563,9 @@
       <c r="Y22" s="56">
         <v>16</v>
       </c>
-      <c r="Z22" s="56"/>
+      <c r="Z22" s="56">
+        <v>17</v>
+      </c>
       <c r="AA22" s="56"/>
       <c r="AB22" s="56"/>
       <c r="AC22" s="56"/>
@@ -8548,11 +8583,11 @@
       <c r="AO22" s="56"/>
       <c r="AP22" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ22" s="71">
         <f t="shared" si="1"/>
-        <v>15.379999999999999</v>
+        <v>15.481249999999999</v>
       </c>
       <c r="AR22" s="71">
         <f>IFERROR(VLOOKUP(A22,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8560,7 +8595,7 @@
       </c>
       <c r="AS22" s="71">
         <f t="shared" si="2"/>
-        <v>1.5996670802315993</v>
+        <v>1.7009170802315996</v>
       </c>
     </row>
     <row r="23" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8639,7 +8674,9 @@
       <c r="Y23" s="56">
         <v>27.5</v>
       </c>
-      <c r="Z23" s="56"/>
+      <c r="Z23" s="56">
+        <v>26.7</v>
+      </c>
       <c r="AA23" s="56"/>
       <c r="AB23" s="56"/>
       <c r="AC23" s="56"/>
@@ -8657,11 +8694,11 @@
       <c r="AO23" s="56"/>
       <c r="AP23" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ23" s="71">
         <f t="shared" si="1"/>
-        <v>26.299999999999997</v>
+        <v>26.324999999999996</v>
       </c>
       <c r="AR23" s="71" t="str">
         <f>IFERROR(VLOOKUP(A23,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8748,7 +8785,9 @@
       <c r="Y24" s="56">
         <v>31.1</v>
       </c>
-      <c r="Z24" s="56"/>
+      <c r="Z24" s="56">
+        <v>31.4</v>
+      </c>
       <c r="AA24" s="56"/>
       <c r="AB24" s="56"/>
       <c r="AC24" s="56"/>
@@ -8766,11 +8805,11 @@
       <c r="AO24" s="56"/>
       <c r="AP24" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ24" s="71">
         <f t="shared" si="1"/>
-        <v>29.286666666666672</v>
+        <v>29.418750000000003</v>
       </c>
       <c r="AR24" s="71">
         <f>IFERROR(VLOOKUP(A24,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8778,7 +8817,7 @@
       </c>
       <c r="AS24" s="71">
         <f t="shared" si="2"/>
-        <v>0.92430818193055231</v>
+        <v>1.0563915152638828</v>
       </c>
     </row>
     <row r="25" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8857,7 +8896,9 @@
       <c r="Y25" s="56">
         <v>22.9</v>
       </c>
-      <c r="Z25" s="56"/>
+      <c r="Z25" s="56">
+        <v>23.8</v>
+      </c>
       <c r="AA25" s="56"/>
       <c r="AB25" s="56"/>
       <c r="AC25" s="56"/>
@@ -8875,11 +8916,11 @@
       <c r="AO25" s="56"/>
       <c r="AP25" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ25" s="71">
         <f t="shared" si="1"/>
-        <v>22.199999999999996</v>
+        <v>22.299999999999997</v>
       </c>
       <c r="AR25" s="71">
         <f>IFERROR(VLOOKUP(A25,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8887,7 +8928,7 @@
       </c>
       <c r="AS25" s="71">
         <f t="shared" si="2"/>
-        <v>2.2665755437977957</v>
+        <v>2.3665755437977971</v>
       </c>
     </row>
     <row r="26" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8966,7 +9007,9 @@
       <c r="Y26" s="56">
         <v>11.7</v>
       </c>
-      <c r="Z26" s="56"/>
+      <c r="Z26" s="56">
+        <v>12.3</v>
+      </c>
       <c r="AA26" s="56"/>
       <c r="AB26" s="56"/>
       <c r="AC26" s="56"/>
@@ -8984,11 +9027,11 @@
       <c r="AO26" s="56"/>
       <c r="AP26" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ26" s="71">
         <f t="shared" si="1"/>
-        <v>11.69333333333333</v>
+        <v>11.731249999999998</v>
       </c>
       <c r="AR26" s="71">
         <f>IFERROR(VLOOKUP(A26,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8996,7 +9039,7 @@
       </c>
       <c r="AS26" s="71">
         <f t="shared" si="2"/>
-        <v>1.3230184331797403</v>
+        <v>1.360935099846408</v>
       </c>
     </row>
     <row r="27" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9075,7 +9118,9 @@
       <c r="Y27" s="56">
         <v>28.6</v>
       </c>
-      <c r="Z27" s="56"/>
+      <c r="Z27" s="56">
+        <v>30.5</v>
+      </c>
       <c r="AA27" s="56"/>
       <c r="AB27" s="56"/>
       <c r="AC27" s="56"/>
@@ -9093,11 +9138,11 @@
       <c r="AO27" s="56"/>
       <c r="AP27" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ27" s="71">
         <f t="shared" si="1"/>
-        <v>28.213333333333331</v>
+        <v>28.356249999999999</v>
       </c>
       <c r="AR27" s="71">
         <f>IFERROR(VLOOKUP(A27,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9105,7 +9150,7 @@
       </c>
       <c r="AS27" s="71">
         <f t="shared" si="2"/>
-        <v>1.2246273637374827</v>
+        <v>1.3675440304041508</v>
       </c>
     </row>
     <row r="28" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9184,7 +9229,9 @@
       <c r="Y28" s="56">
         <v>27.9</v>
       </c>
-      <c r="Z28" s="56"/>
+      <c r="Z28" s="56">
+        <v>28.7</v>
+      </c>
       <c r="AA28" s="56"/>
       <c r="AB28" s="56"/>
       <c r="AC28" s="56"/>
@@ -9202,11 +9249,11 @@
       <c r="AO28" s="56"/>
       <c r="AP28" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ28" s="71">
         <f t="shared" si="1"/>
-        <v>26.240000000000002</v>
+        <v>26.393750000000001</v>
       </c>
       <c r="AR28" s="71">
         <f>IFERROR(VLOOKUP(A28,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9214,7 +9261,7 @@
       </c>
       <c r="AS28" s="71">
         <f t="shared" si="2"/>
-        <v>0.4885814485230604</v>
+        <v>0.64233144852305912</v>
       </c>
     </row>
     <row r="29" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9293,7 +9340,9 @@
       <c r="Y29" s="56">
         <v>28.7</v>
       </c>
-      <c r="Z29" s="56"/>
+      <c r="Z29" s="56">
+        <v>29.9</v>
+      </c>
       <c r="AA29" s="56"/>
       <c r="AB29" s="56"/>
       <c r="AC29" s="56"/>
@@ -9311,11 +9360,11 @@
       <c r="AO29" s="56"/>
       <c r="AP29" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ29" s="71">
         <f t="shared" si="1"/>
-        <v>27.453333333333333</v>
+        <v>27.606249999999999</v>
       </c>
       <c r="AR29" s="71">
         <f>IFERROR(VLOOKUP(A29,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9323,7 +9372,7 @@
       </c>
       <c r="AS29" s="71">
         <f t="shared" si="2"/>
-        <v>0.49929111907609425</v>
+        <v>0.65220778574276039</v>
       </c>
     </row>
     <row r="30" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9402,7 +9451,9 @@
       <c r="Y30" s="56">
         <v>25.3</v>
       </c>
-      <c r="Z30" s="56"/>
+      <c r="Z30" s="56">
+        <v>25.6</v>
+      </c>
       <c r="AA30" s="56"/>
       <c r="AB30" s="56"/>
       <c r="AC30" s="56"/>
@@ -9420,11 +9471,11 @@
       <c r="AO30" s="56"/>
       <c r="AP30" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ30" s="71">
         <f t="shared" si="1"/>
-        <v>25</v>
+        <v>25.037500000000001</v>
       </c>
       <c r="AR30" s="71">
         <f>IFERROR(VLOOKUP(A30,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9432,7 +9483,7 @@
       </c>
       <c r="AS30" s="71">
         <f t="shared" si="2"/>
-        <v>0.48199851687062889</v>
+        <v>0.51949851687063031</v>
       </c>
     </row>
     <row r="31" spans="1:45" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -9511,7 +9562,9 @@
       <c r="Y31" s="98">
         <v>25.4</v>
       </c>
-      <c r="Z31" s="98"/>
+      <c r="Z31" s="98">
+        <v>27.8</v>
+      </c>
       <c r="AA31" s="98"/>
       <c r="AB31" s="98"/>
       <c r="AC31" s="98"/>
@@ -9529,11 +9582,11 @@
       <c r="AO31" s="98"/>
       <c r="AP31" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ31" s="71">
         <f t="shared" si="1"/>
-        <v>26.326666666666661</v>
+        <v>26.418749999999996</v>
       </c>
       <c r="AR31" s="71">
         <f>IFERROR(VLOOKUP(A31,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9541,7 +9594,7 @@
       </c>
       <c r="AS31" s="71">
         <f t="shared" si="2"/>
-        <v>0.95771804062126265</v>
+        <v>1.0498013739545975</v>
       </c>
     </row>
     <row r="32" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9620,7 +9673,9 @@
       <c r="Y32" s="56">
         <v>20.06666666666667</v>
       </c>
-      <c r="Z32" s="56"/>
+      <c r="Z32" s="56">
+        <v>19.866666666666671</v>
+      </c>
       <c r="AA32" s="56"/>
       <c r="AB32" s="56"/>
       <c r="AC32" s="56"/>
@@ -9638,11 +9693,11 @@
       <c r="AO32" s="56"/>
       <c r="AP32" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ32" s="71">
         <f t="shared" si="1"/>
-        <v>20.628888888888888</v>
+        <v>20.581250000000001</v>
       </c>
       <c r="AR32" s="71">
         <f>IFERROR(VLOOKUP(A32,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9650,7 +9705,7 @@
       </c>
       <c r="AS32" s="71">
         <f t="shared" si="2"/>
-        <v>2.9720328367800484</v>
+        <v>2.9243939478911614</v>
       </c>
     </row>
     <row r="33" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9726,8 +9781,12 @@
       <c r="X33" s="56">
         <v>29.1</v>
       </c>
-      <c r="Y33" s="56"/>
-      <c r="Z33" s="56"/>
+      <c r="Y33" s="56">
+        <v>29.7</v>
+      </c>
+      <c r="Z33" s="56">
+        <v>27.65</v>
+      </c>
       <c r="AA33" s="56"/>
       <c r="AB33" s="56"/>
       <c r="AC33" s="56"/>
@@ -9745,19 +9804,19 @@
       <c r="AO33" s="56"/>
       <c r="AP33" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ33" s="71" t="str">
+        <v>16</v>
+      </c>
+      <c r="AQ33" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>28.031249999999996</v>
       </c>
       <c r="AR33" s="71">
         <f>IFERROR(VLOOKUP(A33,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>26.827472081212552</v>
       </c>
-      <c r="AS33" s="71" t="str">
+      <c r="AS33" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1.2037779187874449</v>
       </c>
     </row>
     <row r="34" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9836,7 +9895,9 @@
       <c r="Y34" s="56">
         <v>21.333333333333329</v>
       </c>
-      <c r="Z34" s="56"/>
+      <c r="Z34" s="56">
+        <v>20.93333333333333</v>
+      </c>
       <c r="AA34" s="56"/>
       <c r="AB34" s="56"/>
       <c r="AC34" s="56"/>
@@ -9854,11 +9915,11 @@
       <c r="AO34" s="56"/>
       <c r="AP34" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ34" s="71">
         <f t="shared" si="1"/>
-        <v>21.408888888888892</v>
+        <v>21.37916666666667</v>
       </c>
       <c r="AR34" s="71">
         <f>IFERROR(VLOOKUP(A34,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9866,7 +9927,7 @@
       </c>
       <c r="AS34" s="71">
         <f t="shared" si="2"/>
-        <v>1.6216912972085709</v>
+        <v>1.5919690749863484</v>
       </c>
     </row>
     <row r="35" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9942,8 +10003,12 @@
       <c r="X35" s="56">
         <v>26.1</v>
       </c>
-      <c r="Y35" s="56"/>
-      <c r="Z35" s="56"/>
+      <c r="Y35" s="56">
+        <v>24.65</v>
+      </c>
+      <c r="Z35" s="56">
+        <v>24.6</v>
+      </c>
       <c r="AA35" s="56"/>
       <c r="AB35" s="56"/>
       <c r="AC35" s="56"/>
@@ -9961,19 +10026,19 @@
       <c r="AO35" s="56"/>
       <c r="AP35" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ35" s="71" t="str">
+        <v>16</v>
+      </c>
+      <c r="AQ35" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>24.596875000000004</v>
       </c>
       <c r="AR35" s="71">
         <f>IFERROR(VLOOKUP(A35,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>24.038247899717401</v>
       </c>
-      <c r="AS35" s="71" t="str">
+      <c r="AS35" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>0.5586271002826031</v>
       </c>
     </row>
     <row r="36" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10161,7 +10226,9 @@
       <c r="Y37" s="56">
         <v>27.1</v>
       </c>
-      <c r="Z37" s="56"/>
+      <c r="Z37" s="56">
+        <v>28.3</v>
+      </c>
       <c r="AA37" s="56"/>
       <c r="AB37" s="56"/>
       <c r="AC37" s="56"/>
@@ -10179,11 +10246,11 @@
       <c r="AO37" s="56"/>
       <c r="AP37" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ37" s="71">
         <f t="shared" si="1"/>
-        <v>27.373333333333335</v>
+        <v>27.431250000000002</v>
       </c>
       <c r="AR37" s="71">
         <f>IFERROR(VLOOKUP(A37,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10191,7 +10258,7 @@
       </c>
       <c r="AS37" s="71">
         <f t="shared" si="2"/>
-        <v>1.4871034593959536</v>
+        <v>1.5450201260626208</v>
       </c>
     </row>
     <row r="38" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10268,7 +10335,9 @@
       <c r="Y38" s="56">
         <v>16.100000000000001</v>
       </c>
-      <c r="Z38" s="56"/>
+      <c r="Z38" s="56">
+        <v>16.2</v>
+      </c>
       <c r="AA38" s="56"/>
       <c r="AB38" s="56"/>
       <c r="AC38" s="56"/>
@@ -10286,19 +10355,19 @@
       <c r="AO38" s="56"/>
       <c r="AP38" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ38" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ38" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>16.046666666666663</v>
       </c>
       <c r="AR38" s="71">
         <f>IFERROR(VLOOKUP(A38,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>15.017929006950681</v>
       </c>
-      <c r="AS38" s="71" t="str">
+      <c r="AS38" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1.0287376597159827</v>
       </c>
     </row>
     <row r="39" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10375,7 +10444,9 @@
       <c r="Y39" s="56">
         <v>23</v>
       </c>
-      <c r="Z39" s="56"/>
+      <c r="Z39" s="56">
+        <v>24.666666666666671</v>
+      </c>
       <c r="AA39" s="56"/>
       <c r="AB39" s="56"/>
       <c r="AC39" s="56"/>
@@ -10393,11 +10464,11 @@
       <c r="AO39" s="56"/>
       <c r="AP39" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ39" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ39" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>22.711111111111116</v>
       </c>
       <c r="AR39" s="71" t="str">
         <f>IFERROR(VLOOKUP(A39,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10478,7 +10549,9 @@
       <c r="Y40" s="56">
         <v>25.2</v>
       </c>
-      <c r="Z40" s="56"/>
+      <c r="Z40" s="56">
+        <v>26.733333333333331</v>
+      </c>
       <c r="AA40" s="56"/>
       <c r="AB40" s="56"/>
       <c r="AC40" s="56"/>
@@ -10496,7 +10569,7 @@
       <c r="AO40" s="56"/>
       <c r="AP40" s="58">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ40" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10587,7 +10660,9 @@
       <c r="Y41" s="56">
         <v>19.533333333333331</v>
       </c>
-      <c r="Z41" s="56"/>
+      <c r="Z41" s="56">
+        <v>21.533333333333331</v>
+      </c>
       <c r="AA41" s="56"/>
       <c r="AB41" s="56"/>
       <c r="AC41" s="56"/>
@@ -10605,11 +10680,11 @@
       <c r="AO41" s="56"/>
       <c r="AP41" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ41" s="71">
         <f t="shared" si="1"/>
-        <v>20.693333333333332</v>
+        <v>20.74583333333333</v>
       </c>
       <c r="AR41" s="71">
         <f>IFERROR(VLOOKUP(A41,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10617,7 +10692,7 @@
       </c>
       <c r="AS41" s="71">
         <f t="shared" si="2"/>
-        <v>2.2012241420055929</v>
+        <v>2.2537241420055913</v>
       </c>
     </row>
     <row r="42" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10696,7 +10771,9 @@
       <c r="Y42" s="56">
         <v>28.9</v>
       </c>
-      <c r="Z42" s="56"/>
+      <c r="Z42" s="56">
+        <v>29.55</v>
+      </c>
       <c r="AA42" s="56"/>
       <c r="AB42" s="56"/>
       <c r="AC42" s="56"/>
@@ -10714,11 +10791,11 @@
       <c r="AO42" s="56"/>
       <c r="AP42" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ42" s="71">
         <f t="shared" si="1"/>
-        <v>28.073333333333331</v>
+        <v>28.165624999999999</v>
       </c>
       <c r="AR42" s="71">
         <f>IFERROR(VLOOKUP(A42,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10726,7 +10803,7 @@
       </c>
       <c r="AS42" s="71">
         <f t="shared" si="2"/>
-        <v>0.32064781627505923</v>
+        <v>0.41293948294172722</v>
       </c>
     </row>
     <row r="43" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10801,7 +10878,9 @@
       <c r="Y43" s="56">
         <v>30.55</v>
       </c>
-      <c r="Z43" s="56"/>
+      <c r="Z43" s="56">
+        <v>30.75</v>
+      </c>
       <c r="AA43" s="56"/>
       <c r="AB43" s="56"/>
       <c r="AC43" s="56"/>
@@ -10819,7 +10898,7 @@
       <c r="AO43" s="56"/>
       <c r="AP43" s="58">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ43" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10910,7 +10989,9 @@
       <c r="Y44" s="56">
         <v>31.35</v>
       </c>
-      <c r="Z44" s="56"/>
+      <c r="Z44" s="56">
+        <v>31.2</v>
+      </c>
       <c r="AA44" s="56"/>
       <c r="AB44" s="56"/>
       <c r="AC44" s="56"/>
@@ -10928,11 +11009,11 @@
       <c r="AO44" s="56"/>
       <c r="AP44" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ44" s="71">
         <f t="shared" si="1"/>
-        <v>28.333333333333329</v>
+        <v>28.512499999999996</v>
       </c>
       <c r="AR44" s="71">
         <f>IFERROR(VLOOKUP(A44,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10940,7 +11021,7 @@
       </c>
       <c r="AS44" s="71">
         <f t="shared" si="2"/>
-        <v>0.99098988905050689</v>
+        <v>1.170156555717174</v>
       </c>
     </row>
     <row r="45" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11019,7 +11100,9 @@
       <c r="Y45" s="56">
         <v>29.55</v>
       </c>
-      <c r="Z45" s="56"/>
+      <c r="Z45" s="56">
+        <v>30.05</v>
+      </c>
       <c r="AA45" s="56"/>
       <c r="AB45" s="56"/>
       <c r="AC45" s="56"/>
@@ -11037,11 +11120,11 @@
       <c r="AO45" s="56"/>
       <c r="AP45" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ45" s="71">
         <f t="shared" si="1"/>
-        <v>29.018333333333334</v>
+        <v>29.082812500000003</v>
       </c>
       <c r="AR45" s="71">
         <f>IFERROR(VLOOKUP(A45,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11049,7 +11132,7 @@
       </c>
       <c r="AS45" s="71">
         <f t="shared" si="2"/>
-        <v>1.1121357014358537</v>
+        <v>1.1766148681025221</v>
       </c>
     </row>
     <row r="46" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11120,15 +11203,17 @@
         <v>30.06666666666667</v>
       </c>
       <c r="W46" s="56">
-        <v>29.266666666666669</v>
+        <v>29.2</v>
       </c>
       <c r="X46" s="56">
         <v>31.733333333333331</v>
       </c>
       <c r="Y46" s="56">
-        <v>31.7</v>
-      </c>
-      <c r="Z46" s="56"/>
+        <v>31.666666666666671</v>
+      </c>
+      <c r="Z46" s="56">
+        <v>31.93333333333333</v>
+      </c>
       <c r="AA46" s="56"/>
       <c r="AB46" s="56"/>
       <c r="AC46" s="56"/>
@@ -11146,11 +11231,11 @@
       <c r="AO46" s="56"/>
       <c r="AP46" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ46" s="71">
         <f t="shared" si="1"/>
-        <v>30.217777777777776</v>
+        <v>30.318750000000001</v>
       </c>
       <c r="AR46" s="71">
         <f>IFERROR(VLOOKUP(A46,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11158,7 +11243,7 @@
       </c>
       <c r="AS46" s="71">
         <f t="shared" si="2"/>
-        <v>2.2489019184603869</v>
+        <v>2.349874140682612</v>
       </c>
     </row>
     <row r="47" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11395,7 +11480,9 @@
       <c r="Y49" s="56">
         <v>31.25</v>
       </c>
-      <c r="Z49" s="56"/>
+      <c r="Z49" s="56">
+        <v>30.2</v>
+      </c>
       <c r="AA49" s="56"/>
       <c r="AB49" s="56"/>
       <c r="AC49" s="56"/>
@@ -11413,11 +11500,11 @@
       <c r="AO49" s="56"/>
       <c r="AP49" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ49" s="71">
         <f t="shared" si="1"/>
-        <v>29.66</v>
+        <v>29.693749999999998</v>
       </c>
       <c r="AR49" s="71">
         <f>IFERROR(VLOOKUP(A49,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11425,7 +11512,7 @@
       </c>
       <c r="AS49" s="71">
         <f t="shared" si="2"/>
-        <v>2.3713096539681793</v>
+        <v>2.405059653968177</v>
       </c>
     </row>
     <row r="50" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11690,7 +11777,9 @@
       <c r="Y52" s="56">
         <v>30.65</v>
       </c>
-      <c r="Z52" s="56"/>
+      <c r="Z52" s="56">
+        <v>30.9</v>
+      </c>
       <c r="AA52" s="56"/>
       <c r="AB52" s="56"/>
       <c r="AC52" s="56"/>
@@ -11708,11 +11797,11 @@
       <c r="AO52" s="56"/>
       <c r="AP52" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ52" s="71">
         <f t="shared" si="1"/>
-        <v>29.27</v>
+        <v>29.371874999999999</v>
       </c>
       <c r="AR52" s="71">
         <f>IFERROR(VLOOKUP(A52,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11720,7 +11809,7 @@
       </c>
       <c r="AS52" s="71">
         <f t="shared" si="2"/>
-        <v>1.9107537034094513</v>
+        <v>2.012628703409451</v>
       </c>
     </row>
     <row r="53" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11799,7 +11888,9 @@
       <c r="Y53" s="56">
         <v>31.7</v>
       </c>
-      <c r="Z53" s="56"/>
+      <c r="Z53" s="56">
+        <v>31.8</v>
+      </c>
       <c r="AA53" s="56"/>
       <c r="AB53" s="56"/>
       <c r="AC53" s="56"/>
@@ -11817,11 +11908,11 @@
       <c r="AO53" s="56"/>
       <c r="AP53" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ53" s="71">
         <f t="shared" si="1"/>
-        <v>30.353333333333335</v>
+        <v>30.443750000000001</v>
       </c>
       <c r="AR53" s="71">
         <f>IFERROR(VLOOKUP(A53,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11829,7 +11920,7 @@
       </c>
       <c r="AS53" s="71">
         <f t="shared" si="2"/>
-        <v>1.8551073082669163</v>
+        <v>1.9455239749335824</v>
       </c>
     </row>
     <row r="54" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11896,7 +11987,9 @@
       <c r="Y54" s="56">
         <v>33.200000000000003</v>
       </c>
-      <c r="Z54" s="56"/>
+      <c r="Z54" s="56">
+        <v>33.5</v>
+      </c>
       <c r="AA54" s="56"/>
       <c r="AB54" s="56"/>
       <c r="AC54" s="56"/>
@@ -11914,7 +12007,7 @@
       <c r="AO54" s="56"/>
       <c r="AP54" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ54" s="71" t="str">
         <f t="shared" si="1"/>
@@ -12002,8 +12095,12 @@
       <c r="X55" s="56">
         <v>30.55</v>
       </c>
-      <c r="Y55" s="56"/>
-      <c r="Z55" s="56"/>
+      <c r="Y55" s="56">
+        <v>30.25</v>
+      </c>
+      <c r="Z55" s="56">
+        <v>29.95</v>
+      </c>
       <c r="AA55" s="56"/>
       <c r="AB55" s="56"/>
       <c r="AC55" s="56"/>
@@ -12021,11 +12118,11 @@
       <c r="AO55" s="56"/>
       <c r="AP55" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ55" s="71" t="str">
+        <v>16</v>
+      </c>
+      <c r="AQ55" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>29.978124999999999</v>
       </c>
       <c r="AR55" s="71" t="str">
         <f>IFERROR(VLOOKUP(A55,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12270,7 +12367,9 @@
       <c r="Y58" s="56">
         <v>30.05</v>
       </c>
-      <c r="Z58" s="56"/>
+      <c r="Z58" s="56">
+        <v>32.450000000000003</v>
+      </c>
       <c r="AA58" s="56"/>
       <c r="AB58" s="56"/>
       <c r="AC58" s="99"/>
@@ -12288,11 +12387,11 @@
       <c r="AO58" s="56"/>
       <c r="AP58" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ58" s="71">
         <f t="shared" si="1"/>
-        <v>29.094999999999995</v>
+        <v>29.304687499999996</v>
       </c>
       <c r="AR58" s="71">
         <f>IFERROR(VLOOKUP(A58,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12300,7 +12399,7 @@
       </c>
       <c r="AS58" s="71">
         <f t="shared" si="2"/>
-        <v>0.98078017091783565</v>
+        <v>1.1904676709178368</v>
       </c>
     </row>
     <row r="59" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12357,15 +12456,25 @@
       <c r="S59" s="56">
         <v>24.8</v>
       </c>
-      <c r="T59" s="56"/>
-      <c r="U59" s="56"/>
-      <c r="V59" s="56"/>
-      <c r="W59" s="56"/>
+      <c r="T59" s="56">
+        <v>26.25</v>
+      </c>
+      <c r="U59" s="56">
+        <v>25.5</v>
+      </c>
+      <c r="V59" s="56">
+        <v>24.9</v>
+      </c>
+      <c r="W59" s="56">
+        <v>26.75</v>
+      </c>
       <c r="X59" s="56">
         <v>25.55</v>
       </c>
       <c r="Y59" s="56"/>
-      <c r="Z59" s="56"/>
+      <c r="Z59" s="56">
+        <v>26.5</v>
+      </c>
       <c r="AA59" s="56"/>
       <c r="AB59" s="56"/>
       <c r="AC59" s="56"/>
@@ -12383,7 +12492,7 @@
       <c r="AO59" s="56"/>
       <c r="AP59" s="58">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AQ59" s="71" t="str">
         <f t="shared" si="1"/>
@@ -12459,8 +12568,12 @@
       <c r="T60" s="56">
         <v>27.05</v>
       </c>
-      <c r="U60" s="56"/>
-      <c r="V60" s="56"/>
+      <c r="U60" s="56">
+        <v>26.35</v>
+      </c>
+      <c r="V60" s="56">
+        <v>26.8</v>
+      </c>
       <c r="W60" s="56">
         <v>26.65</v>
       </c>
@@ -12470,7 +12583,9 @@
       <c r="Y60" s="56">
         <v>27</v>
       </c>
-      <c r="Z60" s="56"/>
+      <c r="Z60" s="56">
+        <v>27.3</v>
+      </c>
       <c r="AA60" s="56"/>
       <c r="AB60" s="56"/>
       <c r="AC60" s="56"/>
@@ -12488,19 +12603,19 @@
       <c r="AO60" s="56"/>
       <c r="AP60" s="58">
         <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="AQ60" s="71" t="str">
+        <v>16</v>
+      </c>
+      <c r="AQ60" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>26.525000000000002</v>
       </c>
       <c r="AR60" s="71">
         <f>IFERROR(VLOOKUP(A60,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>25.706671681725961</v>
       </c>
-      <c r="AS60" s="71" t="str">
+      <c r="AS60" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>0.81832831827404107</v>
       </c>
     </row>
     <row r="61" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12579,7 +12694,9 @@
       <c r="Y61" s="56">
         <v>26.6</v>
       </c>
-      <c r="Z61" s="56"/>
+      <c r="Z61" s="56">
+        <v>26.733333333333331</v>
+      </c>
       <c r="AA61" s="56"/>
       <c r="AB61" s="56"/>
       <c r="AC61" s="56"/>
@@ -12597,11 +12714,11 @@
       <c r="AO61" s="56"/>
       <c r="AP61" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ61" s="71">
         <f t="shared" si="1"/>
-        <v>25.617777777777782</v>
+        <v>25.687500000000004</v>
       </c>
       <c r="AR61" s="71">
         <f>IFERROR(VLOOKUP(A61,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12609,7 +12726,7 @@
       </c>
       <c r="AS61" s="71">
         <f t="shared" si="2"/>
-        <v>1.0787738378138911</v>
+        <v>1.1484960600361127</v>
       </c>
     </row>
     <row r="62" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12828,7 +12945,9 @@
       <c r="Y64" s="56">
         <v>25.8</v>
       </c>
-      <c r="Z64" s="56"/>
+      <c r="Z64" s="56">
+        <v>28.3</v>
+      </c>
       <c r="AA64" s="56"/>
       <c r="AB64" s="56"/>
       <c r="AC64" s="56"/>
@@ -12846,7 +12965,7 @@
       <c r="AO64" s="56"/>
       <c r="AP64" s="58">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ64" s="71" t="str">
         <f t="shared" si="1"/>
@@ -12937,7 +13056,9 @@
       <c r="Y65" s="56">
         <v>25.85</v>
       </c>
-      <c r="Z65" s="56"/>
+      <c r="Z65" s="56">
+        <v>27.5</v>
+      </c>
       <c r="AA65" s="56"/>
       <c r="AB65" s="56"/>
       <c r="AC65" s="56"/>
@@ -12955,11 +13076,11 @@
       <c r="AO65" s="56"/>
       <c r="AP65" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ65" s="71">
         <f t="shared" si="1"/>
-        <v>25.513333333333335</v>
+        <v>25.637500000000003</v>
       </c>
       <c r="AR65" s="71">
         <f>IFERROR(VLOOKUP(A65,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12967,7 +13088,7 @@
       </c>
       <c r="AS65" s="71">
         <f t="shared" si="2"/>
-        <v>0.60421850305434432</v>
+        <v>0.72838516972101175</v>
       </c>
     </row>
     <row r="66" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13019,12 +13140,16 @@
       <c r="P66" s="56">
         <v>27.45</v>
       </c>
-      <c r="Q66" s="56"/>
+      <c r="Q66" s="56">
+        <v>24.9</v>
+      </c>
       <c r="R66" s="56"/>
       <c r="S66" s="56">
         <v>24.15</v>
       </c>
-      <c r="T66" s="56"/>
+      <c r="T66" s="56">
+        <v>25.85</v>
+      </c>
       <c r="U66" s="56"/>
       <c r="V66" s="56">
         <v>26.75</v>
@@ -13038,7 +13163,9 @@
       <c r="Y66" s="56">
         <v>25.45</v>
       </c>
-      <c r="Z66" s="56"/>
+      <c r="Z66" s="56">
+        <v>25.45</v>
+      </c>
       <c r="AA66" s="56"/>
       <c r="AB66" s="56"/>
       <c r="AC66" s="56"/>
@@ -13056,7 +13183,7 @@
       <c r="AO66" s="56"/>
       <c r="AP66" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AQ66" s="71" t="str">
         <f t="shared" si="1"/>
@@ -13147,7 +13274,9 @@
       <c r="Y67" s="56">
         <v>25.75</v>
       </c>
-      <c r="Z67" s="56"/>
+      <c r="Z67" s="56">
+        <v>27.55</v>
+      </c>
       <c r="AA67" s="56"/>
       <c r="AB67" s="56"/>
       <c r="AC67" s="56"/>
@@ -13165,11 +13294,11 @@
       <c r="AO67" s="56"/>
       <c r="AP67" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ67" s="71">
         <f t="shared" si="1"/>
-        <v>25.196666666666665</v>
+        <v>25.34375</v>
       </c>
       <c r="AR67" s="71">
         <f>IFERROR(VLOOKUP(A67,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13177,7 +13306,7 @@
       </c>
       <c r="AS67" s="71">
         <f t="shared" si="2"/>
-        <v>0.67157916392364569</v>
+        <v>0.81866249725698026</v>
       </c>
     </row>
     <row r="68" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13218,7 +13347,7 @@
         <v>22.75</v>
       </c>
       <c r="M68" s="56">
-        <v>24.266666666666669</v>
+        <v>24.05</v>
       </c>
       <c r="N68" s="56">
         <v>24.4</v>
@@ -13235,7 +13364,9 @@
       <c r="R68" s="56">
         <v>25.725000000000001</v>
       </c>
-      <c r="S68" s="56"/>
+      <c r="S68" s="56">
+        <v>23.8</v>
+      </c>
       <c r="T68" s="56">
         <v>25.45</v>
       </c>
@@ -13254,7 +13385,9 @@
       <c r="Y68" s="56">
         <v>25.225000000000001</v>
       </c>
-      <c r="Z68" s="56"/>
+      <c r="Z68" s="56">
+        <v>26.05</v>
+      </c>
       <c r="AA68" s="56"/>
       <c r="AB68" s="56"/>
       <c r="AC68" s="56"/>
@@ -13272,19 +13405,19 @@
       <c r="AO68" s="56"/>
       <c r="AP68" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ68" s="71" t="str">
+        <v>16</v>
+      </c>
+      <c r="AQ68" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>24.890625</v>
       </c>
       <c r="AR68" s="71">
         <f>IFERROR(VLOOKUP(A68,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>24.322397686632009</v>
       </c>
-      <c r="AS68" s="71" t="str">
+      <c r="AS68" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>0.56822731336799137</v>
       </c>
     </row>
     <row r="69" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13355,7 +13488,9 @@
       <c r="Y69" s="56">
         <v>26.333333333333329</v>
       </c>
-      <c r="Z69" s="56"/>
+      <c r="Z69" s="56">
+        <v>27.333333333333329</v>
+      </c>
       <c r="AA69" s="56"/>
       <c r="AB69" s="56"/>
       <c r="AC69" s="56"/>
@@ -13373,7 +13508,7 @@
       <c r="AO69" s="56"/>
       <c r="AP69" s="58">
         <f t="shared" ref="AP69:AP132" si="3">COUNTIF(K69:AO69,"&gt;0")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ69" s="71" t="str">
         <f t="shared" ref="AQ69:AQ132" si="4">IF(AP69&gt;14,AVERAGE(K69:AO69),"")</f>
@@ -13464,7 +13599,9 @@
       <c r="Y70" s="56">
         <v>26.8</v>
       </c>
-      <c r="Z70" s="56"/>
+      <c r="Z70" s="56">
+        <v>26.266666666666669</v>
+      </c>
       <c r="AA70" s="56"/>
       <c r="AB70" s="56"/>
       <c r="AC70" s="56"/>
@@ -13482,11 +13619,11 @@
       <c r="AO70" s="56"/>
       <c r="AP70" s="58">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ70" s="71">
         <f t="shared" si="4"/>
-        <v>25.842222222222226</v>
+        <v>25.868750000000002</v>
       </c>
       <c r="AR70" s="71">
         <f>IFERROR(VLOOKUP(A70,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13494,7 +13631,7 @@
       </c>
       <c r="AS70" s="71">
         <f t="shared" si="5"/>
-        <v>0.17977930856869762</v>
+        <v>0.20630708634647377</v>
       </c>
     </row>
     <row r="71" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13558,8 +13695,12 @@
       <c r="T71" s="56">
         <v>26.533333333333331</v>
       </c>
-      <c r="U71" s="56"/>
-      <c r="V71" s="56"/>
+      <c r="U71" s="56">
+        <v>25.63333333333334</v>
+      </c>
+      <c r="V71" s="56">
+        <v>25.233333333333331</v>
+      </c>
       <c r="W71" s="56">
         <v>25.833333333333329</v>
       </c>
@@ -13569,7 +13710,9 @@
       <c r="Y71" s="56">
         <v>26.166666666666671</v>
       </c>
-      <c r="Z71" s="56"/>
+      <c r="Z71" s="56">
+        <v>26.36666666666666</v>
+      </c>
       <c r="AA71" s="56"/>
       <c r="AB71" s="56"/>
       <c r="AC71" s="56"/>
@@ -13587,19 +13730,19 @@
       <c r="AO71" s="56"/>
       <c r="AP71" s="58">
         <f t="shared" si="3"/>
-        <v>13</v>
-      </c>
-      <c r="AQ71" s="71" t="str">
+        <v>16</v>
+      </c>
+      <c r="AQ71" s="71">
         <f t="shared" si="4"/>
-        <v/>
+        <v>25.420833333333338</v>
       </c>
       <c r="AR71" s="71">
         <f>IFERROR(VLOOKUP(A71,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>24.973208742959539</v>
       </c>
-      <c r="AS71" s="71" t="str">
+      <c r="AS71" s="71">
         <f t="shared" si="5"/>
-        <v/>
+        <v>0.44762459037379898</v>
       </c>
     </row>
     <row r="72" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13644,7 +13787,9 @@
       </c>
       <c r="N72" s="56"/>
       <c r="O72" s="56"/>
-      <c r="P72" s="56"/>
+      <c r="P72" s="56">
+        <v>26.4</v>
+      </c>
       <c r="Q72" s="56">
         <v>26.55</v>
       </c>
@@ -13665,8 +13810,12 @@
       <c r="X72" s="56">
         <v>25.2</v>
       </c>
-      <c r="Y72" s="56"/>
-      <c r="Z72" s="56"/>
+      <c r="Y72" s="56">
+        <v>26.3</v>
+      </c>
+      <c r="Z72" s="56">
+        <v>26.15</v>
+      </c>
       <c r="AA72" s="56"/>
       <c r="AB72" s="56"/>
       <c r="AC72" s="56"/>
@@ -13684,7 +13833,7 @@
       <c r="AO72" s="56"/>
       <c r="AP72" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AQ72" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13775,7 +13924,9 @@
       <c r="Y73" s="56">
         <v>21.6</v>
       </c>
-      <c r="Z73" s="56"/>
+      <c r="Z73" s="56">
+        <v>21.35</v>
+      </c>
       <c r="AA73" s="56"/>
       <c r="AB73" s="56"/>
       <c r="AC73" s="56"/>
@@ -13793,11 +13944,11 @@
       <c r="AO73" s="56"/>
       <c r="AP73" s="58">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ73" s="71">
         <f t="shared" si="4"/>
-        <v>20.303333333333335</v>
+        <v>20.368750000000002</v>
       </c>
       <c r="AR73" s="71">
         <f>IFERROR(VLOOKUP(A73,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13805,7 +13956,7 @@
       </c>
       <c r="AS73" s="71">
         <f t="shared" si="5"/>
-        <v>0.30483458397322494</v>
+        <v>0.3702512506398925</v>
       </c>
     </row>
     <row r="74" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13884,7 +14035,9 @@
       <c r="Y74" s="56">
         <v>15.56666666666667</v>
       </c>
-      <c r="Z74" s="56"/>
+      <c r="Z74" s="56">
+        <v>15.66666666666667</v>
+      </c>
       <c r="AA74" s="56"/>
       <c r="AB74" s="56"/>
       <c r="AC74" s="56"/>
@@ -13902,11 +14055,11 @@
       <c r="AO74" s="56"/>
       <c r="AP74" s="58">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ74" s="71">
         <f t="shared" si="4"/>
-        <v>15.428888888888885</v>
+        <v>15.443749999999996</v>
       </c>
       <c r="AR74" s="71">
         <f>IFERROR(VLOOKUP(A74,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13914,7 +14067,7 @@
       </c>
       <c r="AS74" s="71">
         <f t="shared" si="5"/>
-        <v>0.2478451969220945</v>
+        <v>0.26270630803320572</v>
       </c>
     </row>
     <row r="75" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13993,7 +14146,9 @@
       <c r="Y75" s="56">
         <v>20.65</v>
       </c>
-      <c r="Z75" s="56"/>
+      <c r="Z75" s="56">
+        <v>20.45</v>
+      </c>
       <c r="AA75" s="56"/>
       <c r="AB75" s="56"/>
       <c r="AC75" s="56"/>
@@ -14011,11 +14166,11 @@
       <c r="AO75" s="56"/>
       <c r="AP75" s="58">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ75" s="71">
         <f t="shared" si="4"/>
-        <v>20.591666666666665</v>
+        <v>20.582812499999999</v>
       </c>
       <c r="AR75" s="71">
         <f>IFERROR(VLOOKUP(A75,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14023,7 +14178,7 @@
       </c>
       <c r="AS75" s="71">
         <f t="shared" si="5"/>
-        <v>0.79170005514044561</v>
+        <v>0.78284588847377989</v>
       </c>
     </row>
     <row r="76" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14102,7 +14257,9 @@
       <c r="Y76" s="56">
         <v>24.4</v>
       </c>
-      <c r="Z76" s="56"/>
+      <c r="Z76" s="56">
+        <v>25.13333333333334</v>
+      </c>
       <c r="AA76" s="56"/>
       <c r="AB76" s="56"/>
       <c r="AC76" s="56"/>
@@ -14120,11 +14277,11 @@
       <c r="AO76" s="56"/>
       <c r="AP76" s="58">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ76" s="71">
         <f t="shared" si="4"/>
-        <v>23.826666666666661</v>
+        <v>23.908333333333328</v>
       </c>
       <c r="AR76" s="71">
         <f>IFERROR(VLOOKUP(A76,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14132,7 +14289,7 @@
       </c>
       <c r="AS76" s="71">
         <f t="shared" si="5"/>
-        <v>1.1434258106877415</v>
+        <v>1.2250924773544085</v>
       </c>
     </row>
     <row r="77" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14211,7 +14368,9 @@
       <c r="Y77" s="56">
         <v>32.799999999999997</v>
       </c>
-      <c r="Z77" s="56"/>
+      <c r="Z77" s="56">
+        <v>32.200000000000003</v>
+      </c>
       <c r="AA77" s="56"/>
       <c r="AB77" s="56"/>
       <c r="AC77" s="56"/>
@@ -14229,11 +14388,11 @@
       <c r="AO77" s="56"/>
       <c r="AP77" s="58">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ77" s="71">
         <f t="shared" si="4"/>
-        <v>31.049999999999997</v>
+        <v>31.121874999999996</v>
       </c>
       <c r="AR77" s="71">
         <f>IFERROR(VLOOKUP(A77,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14241,7 +14400,7 @@
       </c>
       <c r="AS77" s="71">
         <f t="shared" si="5"/>
-        <v>1.8660701894773482</v>
+        <v>1.9379451894773467</v>
       </c>
     </row>
     <row r="78" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14524,7 +14683,9 @@
       <c r="Y80" s="56">
         <v>24.5</v>
       </c>
-      <c r="Z80" s="56"/>
+      <c r="Z80" s="56">
+        <v>23.45</v>
+      </c>
       <c r="AA80" s="56"/>
       <c r="AB80" s="56"/>
       <c r="AC80" s="56"/>
@@ -14542,19 +14703,19 @@
       <c r="AO80" s="56"/>
       <c r="AP80" s="58">
         <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="AQ80" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ80" s="71">
         <f t="shared" si="4"/>
-        <v/>
+        <v>23.813333333333333</v>
       </c>
       <c r="AR80" s="71">
         <f>IFERROR(VLOOKUP(A80,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>24.17462990609177</v>
       </c>
-      <c r="AS80" s="71" t="str">
+      <c r="AS80" s="71">
         <f t="shared" si="5"/>
-        <v/>
+        <v>-0.36129657275843741</v>
       </c>
     </row>
     <row r="81" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14633,7 +14794,9 @@
       <c r="Y81" s="56">
         <v>26.133333333333329</v>
       </c>
-      <c r="Z81" s="56"/>
+      <c r="Z81" s="56">
+        <v>25.6</v>
+      </c>
       <c r="AA81" s="56"/>
       <c r="AB81" s="56"/>
       <c r="AC81" s="56"/>
@@ -14651,11 +14814,11 @@
       <c r="AO81" s="56"/>
       <c r="AP81" s="58">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ81" s="71">
         <f t="shared" si="4"/>
-        <v>25.482222222222219</v>
+        <v>25.489583333333332</v>
       </c>
       <c r="AR81" s="71">
         <f>IFERROR(VLOOKUP(A81,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14663,7 +14826,7 @@
       </c>
       <c r="AS81" s="71">
         <f t="shared" si="5"/>
-        <v>0.30849976480064001</v>
+        <v>0.31586087591175271</v>
       </c>
     </row>
     <row r="82" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14886,7 +15049,9 @@
       <c r="W84" s="56"/>
       <c r="X84" s="56"/>
       <c r="Y84" s="56"/>
-      <c r="Z84" s="56"/>
+      <c r="Z84" s="56">
+        <v>31.8</v>
+      </c>
       <c r="AA84" s="56"/>
       <c r="AB84" s="56"/>
       <c r="AC84" s="56"/>
@@ -14904,7 +15069,7 @@
       <c r="AO84" s="56"/>
       <c r="AP84" s="58">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ84" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15102,7 +15267,9 @@
       <c r="Y86" s="56">
         <v>35.25</v>
       </c>
-      <c r="Z86" s="56"/>
+      <c r="Z86" s="56">
+        <v>34.549999999999997</v>
+      </c>
       <c r="AA86" s="56"/>
       <c r="AB86" s="56"/>
       <c r="AC86" s="56"/>
@@ -15120,11 +15287,11 @@
       <c r="AO86" s="56"/>
       <c r="AP86" s="58">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ86" s="71">
         <f t="shared" si="4"/>
-        <v>32.36</v>
+        <v>32.496874999999996</v>
       </c>
       <c r="AR86" s="71">
         <f>IFERROR(VLOOKUP(A86,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15132,7 +15299,7 @@
       </c>
       <c r="AS86" s="71">
         <f t="shared" si="5"/>
-        <v>3.3538100275376088</v>
+        <v>3.4906850275376051</v>
       </c>
     </row>
     <row r="87" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15208,8 +15375,12 @@
       <c r="X87" s="56">
         <v>31.3</v>
       </c>
-      <c r="Y87" s="56"/>
-      <c r="Z87" s="56"/>
+      <c r="Y87" s="56">
+        <v>31.55</v>
+      </c>
+      <c r="Z87" s="56">
+        <v>31.6</v>
+      </c>
       <c r="AA87" s="56"/>
       <c r="AB87" s="56"/>
       <c r="AC87" s="56"/>
@@ -15227,19 +15398,19 @@
       <c r="AO87" s="56"/>
       <c r="AP87" s="58">
         <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="AQ87" s="71" t="str">
+        <v>16</v>
+      </c>
+      <c r="AQ87" s="71">
         <f t="shared" si="4"/>
-        <v/>
+        <v>30.409375000000008</v>
       </c>
       <c r="AR87" s="71">
         <f>IFERROR(VLOOKUP(A87,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>28.69087461597541</v>
       </c>
-      <c r="AS87" s="71" t="str">
+      <c r="AS87" s="71">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1.7185003840245976</v>
       </c>
     </row>
     <row r="88" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15312,7 +15483,9 @@
       <c r="Y88" s="56">
         <v>35.85</v>
       </c>
-      <c r="Z88" s="56"/>
+      <c r="Z88" s="56">
+        <v>35.4</v>
+      </c>
       <c r="AA88" s="56"/>
       <c r="AB88" s="56"/>
       <c r="AC88" s="56"/>
@@ -15330,7 +15503,7 @@
       <c r="AO88" s="56"/>
       <c r="AP88" s="58">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ88" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15421,7 +15594,9 @@
       <c r="Y89" s="56">
         <v>33.700000000000003</v>
       </c>
-      <c r="Z89" s="56"/>
+      <c r="Z89" s="56">
+        <v>33</v>
+      </c>
       <c r="AA89" s="56"/>
       <c r="AB89" s="56"/>
       <c r="AC89" s="56"/>
@@ -15439,11 +15614,11 @@
       <c r="AO89" s="56"/>
       <c r="AP89" s="58">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ89" s="71">
         <f t="shared" si="4"/>
-        <v>32.166666666666664</v>
+        <v>32.21875</v>
       </c>
       <c r="AR89" s="71">
         <f>IFERROR(VLOOKUP(A89,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15451,7 +15626,7 @@
       </c>
       <c r="AS89" s="71">
         <f t="shared" si="5"/>
-        <v>3.1316066087540051</v>
+        <v>3.1836899420873408</v>
       </c>
     </row>
     <row r="90" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15530,7 +15705,9 @@
       <c r="Y90" s="56">
         <v>17.25</v>
       </c>
-      <c r="Z90" s="56"/>
+      <c r="Z90" s="56">
+        <v>19.3</v>
+      </c>
       <c r="AA90" s="56"/>
       <c r="AB90" s="56"/>
       <c r="AC90" s="56"/>
@@ -15548,11 +15725,11 @@
       <c r="AO90" s="56"/>
       <c r="AP90" s="58">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ90" s="71">
         <f t="shared" si="4"/>
-        <v>17.766666666666666</v>
+        <v>17.862500000000001</v>
       </c>
       <c r="AR90" s="71">
         <f>IFERROR(VLOOKUP(A90,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15560,7 +15737,7 @@
       </c>
       <c r="AS90" s="71">
         <f t="shared" si="5"/>
-        <v>1.6033225806451945</v>
+        <v>1.6991559139785295</v>
       </c>
     </row>
     <row r="91" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15639,7 +15816,9 @@
       <c r="Y91" s="56">
         <v>24.8</v>
       </c>
-      <c r="Z91" s="56"/>
+      <c r="Z91" s="56">
+        <v>25.466666666666669</v>
+      </c>
       <c r="AA91" s="56"/>
       <c r="AB91" s="56"/>
       <c r="AC91" s="56"/>
@@ -15657,11 +15836,11 @@
       <c r="AO91" s="56"/>
       <c r="AP91" s="58">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ91" s="71">
         <f t="shared" si="4"/>
-        <v>23.679999999999996</v>
+        <v>23.791666666666664</v>
       </c>
       <c r="AR91" s="71">
         <f>IFERROR(VLOOKUP(A91,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15669,7 +15848,7 @@
       </c>
       <c r="AS91" s="71">
         <f t="shared" si="5"/>
-        <v>1.5705121341303752</v>
+        <v>1.6821788007970433</v>
       </c>
     </row>
     <row r="92" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15748,7 +15927,9 @@
       <c r="Y92" s="56">
         <v>17.850000000000001</v>
       </c>
-      <c r="Z92" s="56"/>
+      <c r="Z92" s="56">
+        <v>16.75</v>
+      </c>
       <c r="AA92" s="56"/>
       <c r="AB92" s="56"/>
       <c r="AC92" s="56"/>
@@ -15766,11 +15947,11 @@
       <c r="AO92" s="56"/>
       <c r="AP92" s="58">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ92" s="71">
         <f t="shared" si="4"/>
-        <v>17.501666666666669</v>
+        <v>17.454687500000002</v>
       </c>
       <c r="AR92" s="71">
         <f>IFERROR(VLOOKUP(A92,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15778,7 +15959,7 @@
       </c>
       <c r="AS92" s="71">
         <f t="shared" si="5"/>
-        <v>1.4064395207320999</v>
+        <v>1.3594603540654333</v>
       </c>
     </row>
     <row r="93" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15857,7 +16038,9 @@
       <c r="Y93" s="56">
         <v>15.15</v>
       </c>
-      <c r="Z93" s="56"/>
+      <c r="Z93" s="56">
+        <v>14.85</v>
+      </c>
       <c r="AA93" s="56"/>
       <c r="AB93" s="56"/>
       <c r="AC93" s="56"/>
@@ -15875,11 +16058,11 @@
       <c r="AO93" s="56"/>
       <c r="AP93" s="58">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ93" s="71">
         <f t="shared" si="4"/>
-        <v>14.423333333333334</v>
+        <v>14.45</v>
       </c>
       <c r="AR93" s="71">
         <f>IFERROR(VLOOKUP(A93,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15887,7 +16070,7 @@
       </c>
       <c r="AS93" s="71">
         <f t="shared" si="5"/>
-        <v>0.79052519718147352</v>
+        <v>0.81719186384813902</v>
       </c>
     </row>
     <row r="94" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16124,7 +16307,9 @@
       <c r="Y96" s="56">
         <v>13.6</v>
       </c>
-      <c r="Z96" s="56"/>
+      <c r="Z96" s="56">
+        <v>12.9</v>
+      </c>
       <c r="AA96" s="56"/>
       <c r="AB96" s="56"/>
       <c r="AC96" s="56"/>
@@ -16142,11 +16327,11 @@
       <c r="AO96" s="56"/>
       <c r="AP96" s="58">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ96" s="71">
         <f t="shared" si="4"/>
-        <v>13.146666666666668</v>
+        <v>13.131250000000001</v>
       </c>
       <c r="AR96" s="71" t="str">
         <f>IFERROR(VLOOKUP(A96,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16229,7 +16414,9 @@
       <c r="Y97" s="56">
         <v>15.46666666666667</v>
       </c>
-      <c r="Z97" s="56"/>
+      <c r="Z97" s="56">
+        <v>14.83333333333333</v>
+      </c>
       <c r="AA97" s="56"/>
       <c r="AB97" s="56"/>
       <c r="AC97" s="56"/>
@@ -16247,7 +16434,7 @@
       <c r="AO97" s="56"/>
       <c r="AP97" s="58">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ97" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16332,7 +16519,9 @@
       <c r="Y98" s="56">
         <v>17.266666666666669</v>
       </c>
-      <c r="Z98" s="56"/>
+      <c r="Z98" s="56">
+        <v>14.733333333333331</v>
+      </c>
       <c r="AA98" s="56"/>
       <c r="AB98" s="56"/>
       <c r="AC98" s="56"/>
@@ -16350,7 +16539,7 @@
       <c r="AO98" s="56"/>
       <c r="AP98" s="58">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ98" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16431,7 +16620,9 @@
       <c r="Y99" s="56">
         <v>13.95</v>
       </c>
-      <c r="Z99" s="56"/>
+      <c r="Z99" s="56">
+        <v>13.05</v>
+      </c>
       <c r="AA99" s="56"/>
       <c r="AB99" s="56"/>
       <c r="AC99" s="56"/>
@@ -16449,7 +16640,7 @@
       <c r="AO99" s="56"/>
       <c r="AP99" s="58">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ99" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16536,7 +16727,9 @@
       <c r="Y100" s="56">
         <v>13.53333333333333</v>
       </c>
-      <c r="Z100" s="56"/>
+      <c r="Z100" s="56">
+        <v>12.866666666666671</v>
+      </c>
       <c r="AA100" s="56"/>
       <c r="AB100" s="56"/>
       <c r="AC100" s="56"/>
@@ -16554,7 +16747,7 @@
       <c r="AO100" s="56"/>
       <c r="AP100" s="58">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ100" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16797,7 +16990,9 @@
       <c r="Y103" s="56">
         <v>18.399999999999999</v>
       </c>
-      <c r="Z103" s="56"/>
+      <c r="Z103" s="56">
+        <v>19.06666666666667</v>
+      </c>
       <c r="AA103" s="56"/>
       <c r="AB103" s="56"/>
       <c r="AC103" s="56"/>
@@ -16815,7 +17010,7 @@
       <c r="AO103" s="56"/>
       <c r="AP103" s="58">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ103" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16967,7 +17162,9 @@
       <c r="Y105" s="56">
         <v>15.866666666666671</v>
       </c>
-      <c r="Z105" s="56"/>
+      <c r="Z105" s="56">
+        <v>14.733333333333331</v>
+      </c>
       <c r="AA105" s="56"/>
       <c r="AB105" s="56"/>
       <c r="AC105" s="56"/>
@@ -16985,7 +17182,7 @@
       <c r="AO105" s="56"/>
       <c r="AP105" s="58">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ105" s="71" t="str">
         <f t="shared" si="4"/>
@@ -17076,7 +17273,9 @@
       <c r="Y106" s="56">
         <v>13.65</v>
       </c>
-      <c r="Z106" s="56"/>
+      <c r="Z106" s="56">
+        <v>12.324999999999999</v>
+      </c>
       <c r="AA106" s="56"/>
       <c r="AB106" s="56"/>
       <c r="AC106" s="56"/>
@@ -17094,11 +17293,11 @@
       <c r="AO106" s="56"/>
       <c r="AP106" s="58">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ106" s="71">
         <f t="shared" si="4"/>
-        <v>13.876666666666665</v>
+        <v>13.779687499999998</v>
       </c>
       <c r="AR106" s="71">
         <f>IFERROR(VLOOKUP(A106,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17106,7 +17305,7 @@
       </c>
       <c r="AS106" s="71">
         <f t="shared" si="5"/>
-        <v>-0.35236624806514527</v>
+        <v>-0.44934541473181255</v>
       </c>
     </row>
     <row r="107" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17185,7 +17384,9 @@
       <c r="Y107" s="56">
         <v>14.65</v>
       </c>
-      <c r="Z107" s="56"/>
+      <c r="Z107" s="56">
+        <v>14.7</v>
+      </c>
       <c r="AA107" s="56"/>
       <c r="AB107" s="56"/>
       <c r="AC107" s="56"/>
@@ -17203,11 +17404,11 @@
       <c r="AO107" s="56"/>
       <c r="AP107" s="58">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ107" s="71">
         <f t="shared" si="4"/>
-        <v>14.363333333333333</v>
+        <v>14.384374999999999</v>
       </c>
       <c r="AR107" s="71">
         <f>IFERROR(VLOOKUP(A107,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17215,7 +17416,7 @@
       </c>
       <c r="AS107" s="71">
         <f t="shared" si="5"/>
-        <v>0.64957024582554368</v>
+        <v>0.67061191249220897</v>
       </c>
     </row>
     <row r="108" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17403,7 +17604,9 @@
       <c r="Y109" s="56">
         <v>16.333333333333329</v>
       </c>
-      <c r="Z109" s="56"/>
+      <c r="Z109" s="56">
+        <v>16.133333333333329</v>
+      </c>
       <c r="AA109" s="56"/>
       <c r="AB109" s="56"/>
       <c r="AC109" s="56"/>
@@ -17421,11 +17624,11 @@
       <c r="AO109" s="56"/>
       <c r="AP109" s="58">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ109" s="71">
         <f t="shared" si="4"/>
-        <v>15.742222222222226</v>
+        <v>15.766666666666669</v>
       </c>
       <c r="AR109" s="71">
         <f>IFERROR(VLOOKUP(A109,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17433,7 +17636,7 @@
       </c>
       <c r="AS109" s="71">
         <f t="shared" si="5"/>
-        <v>0.23985869864903719</v>
+        <v>0.26430314309348013</v>
       </c>
     </row>
     <row r="110" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17512,7 +17715,9 @@
       <c r="Y110" s="56">
         <v>17.266666666666669</v>
       </c>
-      <c r="Z110" s="56"/>
+      <c r="Z110" s="56">
+        <v>19.2</v>
+      </c>
       <c r="AA110" s="56"/>
       <c r="AB110" s="56"/>
       <c r="AC110" s="56"/>
@@ -17530,11 +17735,11 @@
       <c r="AO110" s="56"/>
       <c r="AP110" s="58">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ110" s="71">
         <f t="shared" si="4"/>
-        <v>17.497777777777777</v>
+        <v>17.604166666666664</v>
       </c>
       <c r="AR110" s="71">
         <f>IFERROR(VLOOKUP(A110,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17542,7 +17747,7 @@
       </c>
       <c r="AS110" s="71">
         <f t="shared" si="5"/>
-        <v>1.1180815166756979</v>
+        <v>1.2244704055645848</v>
       </c>
     </row>
     <row r="111" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17619,7 +17824,9 @@
       <c r="Y111" s="56">
         <v>19.93333333333333</v>
       </c>
-      <c r="Z111" s="56"/>
+      <c r="Z111" s="56">
+        <v>19.86666666666666</v>
+      </c>
       <c r="AA111" s="56"/>
       <c r="AB111" s="56"/>
       <c r="AC111" s="56"/>
@@ -17637,19 +17844,19 @@
       <c r="AO111" s="56"/>
       <c r="AP111" s="58">
         <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="AQ111" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ111" s="71">
         <f t="shared" si="4"/>
-        <v/>
+        <v>18.826666666666668</v>
       </c>
       <c r="AR111" s="71">
         <f>IFERROR(VLOOKUP(A111,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>18.124387467556531</v>
       </c>
-      <c r="AS111" s="71" t="str">
+      <c r="AS111" s="71">
         <f t="shared" si="5"/>
-        <v/>
+        <v>0.70227919911013714</v>
       </c>
     </row>
     <row r="112" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17819,7 +18026,9 @@
       <c r="Y113" s="56">
         <v>27.4</v>
       </c>
-      <c r="Z113" s="56"/>
+      <c r="Z113" s="56">
+        <v>28.2</v>
+      </c>
       <c r="AA113" s="56"/>
       <c r="AB113" s="56"/>
       <c r="AC113" s="56"/>
@@ -17837,11 +18046,11 @@
       <c r="AO113" s="56"/>
       <c r="AP113" s="58">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ113" s="71">
         <f t="shared" si="4"/>
-        <v>26.026666666666667</v>
+        <v>26.162500000000001</v>
       </c>
       <c r="AR113" s="71">
         <f>IFERROR(VLOOKUP(A113,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17849,7 +18058,7 @@
       </c>
       <c r="AS113" s="71">
         <f t="shared" si="5"/>
-        <v>0.18218668891364587</v>
+        <v>0.31802002224698001</v>
       </c>
     </row>
     <row r="114" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17928,7 +18137,9 @@
       <c r="Y114" s="56">
         <v>19.600000000000001</v>
       </c>
-      <c r="Z114" s="56"/>
+      <c r="Z114" s="56">
+        <v>19.8</v>
+      </c>
       <c r="AA114" s="56"/>
       <c r="AB114" s="56"/>
       <c r="AC114" s="56"/>
@@ -17946,11 +18157,11 @@
       <c r="AO114" s="56"/>
       <c r="AP114" s="58">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ114" s="71">
         <f t="shared" si="4"/>
-        <v>19.164444444444442</v>
+        <v>19.204166666666666</v>
       </c>
       <c r="AR114" s="71">
         <f>IFERROR(VLOOKUP(A114,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17958,7 +18169,7 @@
       </c>
       <c r="AS114" s="71">
         <f t="shared" si="5"/>
-        <v>0.76793927810362206</v>
+        <v>0.80766150032584605</v>
       </c>
     </row>
     <row r="115" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18037,7 +18248,9 @@
       <c r="Y115" s="56">
         <v>28.733333333333331</v>
       </c>
-      <c r="Z115" s="56"/>
+      <c r="Z115" s="56">
+        <v>27.933333333333341</v>
+      </c>
       <c r="AA115" s="56"/>
       <c r="AB115" s="56"/>
       <c r="AC115" s="56"/>
@@ -18055,11 +18268,11 @@
       <c r="AO115" s="56"/>
       <c r="AP115" s="58">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ115" s="71">
         <f t="shared" si="4"/>
-        <v>26.151111111111117</v>
+        <v>26.262500000000006</v>
       </c>
       <c r="AR115" s="71">
         <f>IFERROR(VLOOKUP(A115,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18067,7 +18280,7 @@
       </c>
       <c r="AS115" s="71">
         <f t="shared" si="5"/>
-        <v>0.78227150537636803</v>
+        <v>0.89366039426525745</v>
       </c>
     </row>
     <row r="116" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18146,7 +18359,9 @@
       <c r="Y116" s="56">
         <v>29.6</v>
       </c>
-      <c r="Z116" s="56"/>
+      <c r="Z116" s="56">
+        <v>29.666666666666671</v>
+      </c>
       <c r="AA116" s="56"/>
       <c r="AB116" s="56"/>
       <c r="AC116" s="56"/>
@@ -18164,11 +18379,11 @@
       <c r="AO116" s="56"/>
       <c r="AP116" s="58">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ116" s="71">
         <f t="shared" si="4"/>
-        <v>28.382222222222229</v>
+        <v>28.462500000000006</v>
       </c>
       <c r="AR116" s="71">
         <f>IFERROR(VLOOKUP(A116,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18176,7 +18391,7 @@
       </c>
       <c r="AS116" s="71">
         <f t="shared" si="5"/>
-        <v>2.6289426523297692</v>
+        <v>2.7092204301075462</v>
       </c>
     </row>
     <row r="117" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18255,7 +18470,9 @@
       <c r="Y117" s="56">
         <v>23.666666666666671</v>
       </c>
-      <c r="Z117" s="56"/>
+      <c r="Z117" s="56">
+        <v>24.733333333333331</v>
+      </c>
       <c r="AA117" s="56"/>
       <c r="AB117" s="56"/>
       <c r="AC117" s="56"/>
@@ -18273,11 +18490,11 @@
       <c r="AO117" s="56"/>
       <c r="AP117" s="58">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ117" s="71">
         <f t="shared" si="4"/>
-        <v>23.20888888888889</v>
+        <v>23.304166666666667</v>
       </c>
       <c r="AR117" s="71">
         <f>IFERROR(VLOOKUP(A117,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18285,7 +18502,7 @@
       </c>
       <c r="AS117" s="71">
         <f t="shared" si="5"/>
-        <v>1.4804480286738801</v>
+        <v>1.5757258064516577</v>
       </c>
     </row>
     <row r="118" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18354,7 +18571,9 @@
       <c r="Y118" s="56">
         <v>28</v>
       </c>
-      <c r="Z118" s="56"/>
+      <c r="Z118" s="56">
+        <v>28.8</v>
+      </c>
       <c r="AA118" s="56"/>
       <c r="AB118" s="56"/>
       <c r="AC118" s="56"/>
@@ -18372,7 +18591,7 @@
       <c r="AO118" s="56"/>
       <c r="AP118" s="58">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ118" s="71" t="str">
         <f t="shared" si="4"/>
@@ -18539,8 +18758,12 @@
       <c r="X120" s="56">
         <v>12.866666666666671</v>
       </c>
-      <c r="Y120" s="56"/>
-      <c r="Z120" s="56"/>
+      <c r="Y120" s="56">
+        <v>12.733333333333331</v>
+      </c>
+      <c r="Z120" s="56">
+        <v>13.133333333333329</v>
+      </c>
       <c r="AA120" s="56"/>
       <c r="AB120" s="56"/>
       <c r="AC120" s="56"/>
@@ -18558,19 +18781,19 @@
       <c r="AO120" s="56"/>
       <c r="AP120" s="58">
         <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="AQ120" s="71" t="str">
+        <v>16</v>
+      </c>
+      <c r="AQ120" s="71">
         <f t="shared" si="4"/>
-        <v/>
+        <v>12.222916666666666</v>
       </c>
       <c r="AR120" s="71">
         <f>IFERROR(VLOOKUP(A120,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>10.302756995970279</v>
       </c>
-      <c r="AS120" s="71" t="str">
+      <c r="AS120" s="71">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1.9201596706963873</v>
       </c>
     </row>
     <row r="121" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18726,7 +18949,9 @@
       <c r="Y122" s="56">
         <v>15.866666666666671</v>
       </c>
-      <c r="Z122" s="56"/>
+      <c r="Z122" s="56">
+        <v>16</v>
+      </c>
       <c r="AA122" s="56"/>
       <c r="AB122" s="56"/>
       <c r="AC122" s="56"/>
@@ -18744,19 +18969,19 @@
       <c r="AO122" s="56"/>
       <c r="AP122" s="58">
         <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="AQ122" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ122" s="71">
         <f t="shared" si="4"/>
-        <v/>
+        <v>15.582222222222221</v>
       </c>
       <c r="AR122" s="71">
         <f>IFERROR(VLOOKUP(A122,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>15.04905895954351</v>
       </c>
-      <c r="AS122" s="71" t="str">
+      <c r="AS122" s="71">
         <f t="shared" si="5"/>
-        <v/>
+        <v>0.53316326267871084</v>
       </c>
     </row>
     <row r="123" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18904,7 +19129,9 @@
       <c r="Y124" s="56">
         <v>11.866666666666671</v>
       </c>
-      <c r="Z124" s="56"/>
+      <c r="Z124" s="56">
+        <v>12.733333333333331</v>
+      </c>
       <c r="AA124" s="56"/>
       <c r="AB124" s="56"/>
       <c r="AC124" s="56"/>
@@ -18922,7 +19149,7 @@
       <c r="AO124" s="56"/>
       <c r="AP124" s="58">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ124" s="71" t="str">
         <f t="shared" si="4"/>
@@ -19250,7 +19477,9 @@
       <c r="Y128" s="56">
         <v>16.333333333333329</v>
       </c>
-      <c r="Z128" s="56"/>
+      <c r="Z128" s="56">
+        <v>16.533333333333331</v>
+      </c>
       <c r="AA128" s="56"/>
       <c r="AB128" s="56"/>
       <c r="AC128" s="56"/>
@@ -19268,11 +19497,11 @@
       <c r="AO128" s="56"/>
       <c r="AP128" s="58">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ128" s="71">
         <f t="shared" si="4"/>
-        <v>15.904444444444444</v>
+        <v>15.94375</v>
       </c>
       <c r="AR128" s="71">
         <f>IFERROR(VLOOKUP(A128,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19280,7 +19509,7 @@
       </c>
       <c r="AS128" s="71">
         <f t="shared" si="5"/>
-        <v>1.6512020699769945</v>
+        <v>1.6905076255325504</v>
       </c>
     </row>
     <row r="129" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19356,8 +19585,12 @@
       <c r="X129" s="56">
         <v>18.850000000000001</v>
       </c>
-      <c r="Y129" s="56"/>
-      <c r="Z129" s="56"/>
+      <c r="Y129" s="56">
+        <v>18.7</v>
+      </c>
+      <c r="Z129" s="56">
+        <v>19.5</v>
+      </c>
       <c r="AA129" s="56"/>
       <c r="AB129" s="56"/>
       <c r="AC129" s="56"/>
@@ -19375,19 +19608,19 @@
       <c r="AO129" s="56"/>
       <c r="AP129" s="58">
         <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="AQ129" s="71" t="str">
+        <v>16</v>
+      </c>
+      <c r="AQ129" s="71">
         <f t="shared" si="4"/>
-        <v/>
+        <v>18.418749999999999</v>
       </c>
       <c r="AR129" s="71">
         <f>IFERROR(VLOOKUP(A129,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>16.792896998903949</v>
       </c>
-      <c r="AS129" s="71" t="str">
+      <c r="AS129" s="71">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1.6258530010960506</v>
       </c>
     </row>
     <row r="130" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19545,7 +19778,9 @@
       <c r="Y131" s="56">
         <v>14.1</v>
       </c>
-      <c r="Z131" s="56"/>
+      <c r="Z131" s="56">
+        <v>15.133333333333329</v>
+      </c>
       <c r="AA131" s="56"/>
       <c r="AB131" s="56"/>
       <c r="AC131" s="56"/>
@@ -19563,11 +19798,11 @@
       <c r="AO131" s="56"/>
       <c r="AP131" s="58">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ131" s="71">
         <f t="shared" si="4"/>
-        <v>13.96</v>
+        <v>14.033333333333333</v>
       </c>
       <c r="AR131" s="71">
         <f>IFERROR(VLOOKUP(A131,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19575,7 +19810,7 @@
       </c>
       <c r="AS131" s="71">
         <f t="shared" si="5"/>
-        <v>1.324660225346161</v>
+        <v>1.3979935586794934</v>
       </c>
     </row>
     <row r="132" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19654,7 +19889,9 @@
       <c r="Y132" s="56">
         <v>18.466666666666669</v>
       </c>
-      <c r="Z132" s="56"/>
+      <c r="Z132" s="56">
+        <v>18.2</v>
+      </c>
       <c r="AA132" s="56"/>
       <c r="AB132" s="56"/>
       <c r="AC132" s="56"/>
@@ -19672,11 +19909,11 @@
       <c r="AO132" s="56"/>
       <c r="AP132" s="58">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ132" s="71">
         <f t="shared" si="4"/>
-        <v>17.968888888888888</v>
+        <v>17.983333333333331</v>
       </c>
       <c r="AR132" s="71">
         <f>IFERROR(VLOOKUP(A132,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19684,7 +19921,7 @@
       </c>
       <c r="AS132" s="71">
         <f t="shared" si="5"/>
-        <v>2.3867100465052182</v>
+        <v>2.4011544909496614</v>
       </c>
     </row>
     <row r="133" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19763,7 +20000,9 @@
       <c r="Y133" s="56">
         <v>22.55</v>
       </c>
-      <c r="Z133" s="56"/>
+      <c r="Z133" s="56">
+        <v>22.3</v>
+      </c>
       <c r="AA133" s="56"/>
       <c r="AB133" s="56"/>
       <c r="AC133" s="56"/>
@@ -19781,11 +20020,11 @@
       <c r="AO133" s="56"/>
       <c r="AP133" s="58">
         <f t="shared" ref="AP133:AP196" si="6">COUNTIF(K133:AO133,"&gt;0")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ133" s="71">
         <f t="shared" ref="AQ133:AQ196" si="7">IF(AP133&gt;14,AVERAGE(K133:AO133),"")</f>
-        <v>21.083333333333332</v>
+        <v>21.159375000000001</v>
       </c>
       <c r="AR133" s="71">
         <f>IFERROR(VLOOKUP(A133,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19793,7 +20032,7 @@
       </c>
       <c r="AS133" s="71">
         <f t="shared" ref="AS133:AS196" si="8">IF(OR(AQ133="",AR133=""),"",IFERROR(AQ133-AR133,""))</f>
-        <v>2.401452695928203</v>
+        <v>2.4774943625948715</v>
       </c>
     </row>
     <row r="134" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20387,7 +20626,9 @@
       <c r="Y139" s="56">
         <v>14.266666666666669</v>
       </c>
-      <c r="Z139" s="56"/>
+      <c r="Z139" s="56">
+        <v>13.8</v>
+      </c>
       <c r="AA139" s="56"/>
       <c r="AB139" s="56"/>
       <c r="AC139" s="56"/>
@@ -20405,11 +20646,11 @@
       <c r="AO139" s="56"/>
       <c r="AP139" s="58">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ139" s="71">
         <f t="shared" si="7"/>
-        <v>13.586666666666668</v>
+        <v>13.600000000000001</v>
       </c>
       <c r="AR139" s="71">
         <f>IFERROR(VLOOKUP(A139,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20417,7 +20658,7 @@
       </c>
       <c r="AS139" s="71">
         <f t="shared" si="8"/>
-        <v>1.5726372698286184</v>
+        <v>1.585970603161952</v>
       </c>
     </row>
     <row r="140" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20712,7 +20953,9 @@
       <c r="Y142" s="56">
         <v>16.13333333333334</v>
       </c>
-      <c r="Z142" s="56"/>
+      <c r="Z142" s="56">
+        <v>14.8</v>
+      </c>
       <c r="AA142" s="56"/>
       <c r="AB142" s="56"/>
       <c r="AC142" s="56"/>
@@ -20730,11 +20973,11 @@
       <c r="AO142" s="56"/>
       <c r="AP142" s="58">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ142" s="71">
         <f t="shared" si="7"/>
-        <v>15.653333333333334</v>
+        <v>15.600000000000001</v>
       </c>
       <c r="AR142" s="71">
         <f>IFERROR(VLOOKUP(A142,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20742,7 +20985,7 @@
       </c>
       <c r="AS142" s="71">
         <f t="shared" si="8"/>
-        <v>-5.9552420580955001E-2</v>
+        <v>-0.11288575391428779</v>
       </c>
     </row>
     <row r="143" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20821,7 +21064,9 @@
       <c r="Y143" s="56">
         <v>20.2</v>
       </c>
-      <c r="Z143" s="56"/>
+      <c r="Z143" s="56">
+        <v>19.266666666666669</v>
+      </c>
       <c r="AA143" s="56"/>
       <c r="AB143" s="56"/>
       <c r="AC143" s="56"/>
@@ -20839,11 +21084,11 @@
       <c r="AO143" s="56"/>
       <c r="AP143" s="58">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ143" s="71">
         <f t="shared" si="7"/>
-        <v>19.373333333333331</v>
+        <v>19.366666666666664</v>
       </c>
       <c r="AR143" s="71">
         <f>IFERROR(VLOOKUP(A143,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20851,7 +21096,7 @@
       </c>
       <c r="AS143" s="71">
         <f t="shared" si="8"/>
-        <v>0.33131679883521059</v>
+        <v>0.32465013216854288</v>
       </c>
     </row>
     <row r="144" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20930,7 +21175,9 @@
       <c r="Y144" s="56">
         <v>31.533333333333331</v>
       </c>
-      <c r="Z144" s="56"/>
+      <c r="Z144" s="56">
+        <v>30.666666666666671</v>
+      </c>
       <c r="AA144" s="56"/>
       <c r="AB144" s="56"/>
       <c r="AC144" s="56"/>
@@ -20948,11 +21195,11 @@
       <c r="AO144" s="56"/>
       <c r="AP144" s="58">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ144" s="71">
         <f t="shared" si="7"/>
-        <v>30.066666666666666</v>
+        <v>30.104166666666668</v>
       </c>
       <c r="AR144" s="71">
         <f>IFERROR(VLOOKUP(A144,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20960,7 +21207,7 @@
       </c>
       <c r="AS144" s="71">
         <f t="shared" si="8"/>
-        <v>1.3094671288694357</v>
+        <v>1.3469671288694371</v>
       </c>
     </row>
     <row r="145" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21039,7 +21286,9 @@
       <c r="Y145" s="56">
         <v>26</v>
       </c>
-      <c r="Z145" s="56"/>
+      <c r="Z145" s="56">
+        <v>25.733333333333331</v>
+      </c>
       <c r="AA145" s="56"/>
       <c r="AB145" s="56"/>
       <c r="AC145" s="56"/>
@@ -21057,11 +21306,11 @@
       <c r="AO145" s="56"/>
       <c r="AP145" s="58">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ145" s="71">
         <f t="shared" si="7"/>
-        <v>25.048888888888893</v>
+        <v>25.091666666666672</v>
       </c>
       <c r="AR145" s="71">
         <f>IFERROR(VLOOKUP(A145,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21069,7 +21318,7 @@
       </c>
       <c r="AS145" s="71">
         <f t="shared" si="8"/>
-        <v>1.5448313970255327</v>
+        <v>1.5876091748033119</v>
       </c>
     </row>
     <row r="146" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21255,7 +21504,9 @@
       <c r="Y147" s="56">
         <v>24.6</v>
       </c>
-      <c r="Z147" s="56"/>
+      <c r="Z147" s="56">
+        <v>24.93333333333333</v>
+      </c>
       <c r="AA147" s="56"/>
       <c r="AB147" s="56"/>
       <c r="AC147" s="56"/>
@@ -21273,11 +21524,11 @@
       <c r="AO147" s="56"/>
       <c r="AP147" s="58">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ147" s="71">
         <f t="shared" si="7"/>
-        <v>23.604444444444443</v>
+        <v>23.6875</v>
       </c>
       <c r="AR147" s="71">
         <f>IFERROR(VLOOKUP(A147,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21285,7 +21536,7 @@
       </c>
       <c r="AS147" s="71">
         <f t="shared" si="8"/>
-        <v>1.728376671491592</v>
+        <v>1.811432227047149</v>
       </c>
     </row>
     <row r="148" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21443,7 +21694,9 @@
       <c r="Y149" s="56">
         <v>24.933333333333341</v>
       </c>
-      <c r="Z149" s="56"/>
+      <c r="Z149" s="56">
+        <v>23</v>
+      </c>
       <c r="AA149" s="56"/>
       <c r="AB149" s="56"/>
       <c r="AC149" s="56"/>
@@ -21461,11 +21714,11 @@
       <c r="AO149" s="56"/>
       <c r="AP149" s="58">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ149" s="71">
         <f t="shared" si="7"/>
-        <v>23.544444444444444</v>
+        <v>23.510416666666668</v>
       </c>
       <c r="AR149" s="71">
         <f>IFERROR(VLOOKUP(A149,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21473,7 +21726,7 @@
       </c>
       <c r="AS149" s="71">
         <f t="shared" si="8"/>
-        <v>1.7318571658238042</v>
+        <v>1.6978293880460278</v>
       </c>
     </row>
     <row r="150" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21710,7 +21963,9 @@
       <c r="Y152" s="56">
         <v>21.05</v>
       </c>
-      <c r="Z152" s="56"/>
+      <c r="Z152" s="56">
+        <v>21.4</v>
+      </c>
       <c r="AA152" s="56"/>
       <c r="AB152" s="56"/>
       <c r="AC152" s="56"/>
@@ -21728,11 +21983,11 @@
       <c r="AO152" s="56"/>
       <c r="AP152" s="58">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ152" s="71">
         <f t="shared" si="7"/>
-        <v>20.64</v>
+        <v>20.6875</v>
       </c>
       <c r="AR152" s="71">
         <f>IFERROR(VLOOKUP(A152,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21740,7 +21995,7 @@
       </c>
       <c r="AS152" s="71">
         <f t="shared" si="8"/>
-        <v>1.1263792456050616</v>
+        <v>1.1738792456050611</v>
       </c>
     </row>
     <row r="153" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21819,7 +22074,9 @@
       <c r="Y153" s="56">
         <v>30.666666666666671</v>
       </c>
-      <c r="Z153" s="56"/>
+      <c r="Z153" s="56">
+        <v>31.466666666666669</v>
+      </c>
       <c r="AA153" s="56"/>
       <c r="AB153" s="56"/>
       <c r="AC153" s="56"/>
@@ -21837,11 +22094,11 @@
       <c r="AO153" s="56"/>
       <c r="AP153" s="58">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ153" s="71">
         <f t="shared" si="7"/>
-        <v>28.808888888888891</v>
+        <v>28.975000000000001</v>
       </c>
       <c r="AR153" s="71">
         <f>IFERROR(VLOOKUP(A153,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21849,7 +22106,7 @@
       </c>
       <c r="AS153" s="71">
         <f t="shared" si="8"/>
-        <v>1.0861023280330926</v>
+        <v>1.252213439144203</v>
       </c>
     </row>
     <row r="154" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22001,7 +22258,9 @@
       <c r="Y155" s="56">
         <v>31.333333333333329</v>
       </c>
-      <c r="Z155" s="56"/>
+      <c r="Z155" s="56">
+        <v>31.866666666666671</v>
+      </c>
       <c r="AA155" s="56"/>
       <c r="AB155" s="56"/>
       <c r="AC155" s="56"/>
@@ -22019,7 +22278,7 @@
       <c r="AO155" s="56"/>
       <c r="AP155" s="58">
         <f t="shared" si="6"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ155" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22106,7 +22365,9 @@
       <c r="Y156" s="56">
         <v>31.266666666666669</v>
       </c>
-      <c r="Z156" s="56"/>
+      <c r="Z156" s="56">
+        <v>32.266666666666673</v>
+      </c>
       <c r="AA156" s="56"/>
       <c r="AB156" s="56"/>
       <c r="AC156" s="56"/>
@@ -22124,7 +22385,7 @@
       <c r="AO156" s="56"/>
       <c r="AP156" s="58">
         <f t="shared" si="6"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ156" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22211,7 +22472,9 @@
       <c r="Y157" s="56">
         <v>22.06666666666667</v>
       </c>
-      <c r="Z157" s="56"/>
+      <c r="Z157" s="56">
+        <v>21.466666666666669</v>
+      </c>
       <c r="AA157" s="56"/>
       <c r="AB157" s="56"/>
       <c r="AC157" s="56"/>
@@ -22229,7 +22492,7 @@
       <c r="AO157" s="56"/>
       <c r="AP157" s="58">
         <f t="shared" si="6"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ157" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22320,7 +22583,9 @@
       <c r="Y158" s="56">
         <v>27.466666666666669</v>
       </c>
-      <c r="Z158" s="56"/>
+      <c r="Z158" s="56">
+        <v>28.733333333333331</v>
+      </c>
       <c r="AA158" s="56"/>
       <c r="AB158" s="56"/>
       <c r="AC158" s="56"/>
@@ -22338,11 +22603,11 @@
       <c r="AO158" s="56"/>
       <c r="AP158" s="58">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ158" s="71">
         <f t="shared" si="7"/>
-        <v>27.102222222222228</v>
+        <v>27.204166666666673</v>
       </c>
       <c r="AR158" s="71" t="str">
         <f>IFERROR(VLOOKUP(A158,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22413,7 +22678,9 @@
       <c r="Y159" s="56">
         <v>20.93333333333333</v>
       </c>
-      <c r="Z159" s="56"/>
+      <c r="Z159" s="56">
+        <v>20.8</v>
+      </c>
       <c r="AA159" s="56"/>
       <c r="AB159" s="56"/>
       <c r="AC159" s="56"/>
@@ -22431,7 +22698,7 @@
       <c r="AO159" s="56"/>
       <c r="AP159" s="58">
         <f t="shared" si="6"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ159" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22522,7 +22789,9 @@
       <c r="Y160" s="56">
         <v>29.466666666666669</v>
       </c>
-      <c r="Z160" s="56"/>
+      <c r="Z160" s="56">
+        <v>30.466666666666669</v>
+      </c>
       <c r="AA160" s="56"/>
       <c r="AB160" s="56"/>
       <c r="AC160" s="56"/>
@@ -22540,11 +22809,11 @@
       <c r="AO160" s="56"/>
       <c r="AP160" s="58">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ160" s="71">
         <f t="shared" si="7"/>
-        <v>29.053333333333331</v>
+        <v>29.141666666666666</v>
       </c>
       <c r="AR160" s="71">
         <f>IFERROR(VLOOKUP(A160,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22552,7 +22821,7 @@
       </c>
       <c r="AS160" s="71">
         <f t="shared" si="8"/>
-        <v>0.47979594545905258</v>
+        <v>0.56812927879238728</v>
       </c>
     </row>
     <row r="161" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22631,7 +22900,9 @@
       <c r="Y161" s="56">
         <v>22.13333333333334</v>
       </c>
-      <c r="Z161" s="56"/>
+      <c r="Z161" s="56">
+        <v>22</v>
+      </c>
       <c r="AA161" s="56"/>
       <c r="AB161" s="56"/>
       <c r="AC161" s="56"/>
@@ -22649,11 +22920,11 @@
       <c r="AO161" s="56"/>
       <c r="AP161" s="58">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ161" s="71">
         <f t="shared" si="7"/>
-        <v>21.506666666666664</v>
+        <v>21.537499999999998</v>
       </c>
       <c r="AR161" s="71">
         <f>IFERROR(VLOOKUP(A161,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22661,7 +22932,7 @@
       </c>
       <c r="AS161" s="71">
         <f t="shared" si="8"/>
-        <v>0.25724285106608491</v>
+        <v>0.28807618439941862</v>
       </c>
     </row>
     <row r="162" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23033,7 +23304,9 @@
       <c r="Y165" s="56">
         <v>22</v>
       </c>
-      <c r="Z165" s="56"/>
+      <c r="Z165" s="56">
+        <v>22</v>
+      </c>
       <c r="AA165" s="56"/>
       <c r="AB165" s="56"/>
       <c r="AC165" s="56"/>
@@ -23051,7 +23324,7 @@
       <c r="AO165" s="56"/>
       <c r="AP165" s="58">
         <f t="shared" si="6"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ165" s="71" t="str">
         <f t="shared" si="7"/>
@@ -23142,7 +23415,9 @@
       <c r="Y166" s="56">
         <v>29.15</v>
       </c>
-      <c r="Z166" s="56"/>
+      <c r="Z166" s="56">
+        <v>30.3</v>
+      </c>
       <c r="AA166" s="56"/>
       <c r="AB166" s="56"/>
       <c r="AC166" s="56"/>
@@ -23160,11 +23435,11 @@
       <c r="AO166" s="56"/>
       <c r="AP166" s="58">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ166" s="71">
         <f t="shared" si="7"/>
-        <v>28.20333333333333</v>
+        <v>28.334374999999998</v>
       </c>
       <c r="AR166" s="71">
         <f>IFERROR(VLOOKUP(A166,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23172,7 +23447,7 @@
       </c>
       <c r="AS166" s="71">
         <f t="shared" si="8"/>
-        <v>2.137468867266751</v>
+        <v>2.2685105339334193</v>
       </c>
     </row>
     <row r="167" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23251,7 +23526,9 @@
       <c r="Y167" s="56">
         <v>8.8500000000000014</v>
       </c>
-      <c r="Z167" s="56"/>
+      <c r="Z167" s="56">
+        <v>9</v>
+      </c>
       <c r="AA167" s="56"/>
       <c r="AB167" s="56"/>
       <c r="AC167" s="56"/>
@@ -23269,11 +23546,11 @@
       <c r="AO167" s="56"/>
       <c r="AP167" s="58">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ167" s="71">
         <f t="shared" si="7"/>
-        <v>8.7766666666666655</v>
+        <v>8.7906249999999986</v>
       </c>
       <c r="AR167" s="71">
         <f>IFERROR(VLOOKUP(A167,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23281,7 +23558,7 @@
       </c>
       <c r="AS167" s="71">
         <f t="shared" si="8"/>
-        <v>0.23454238531212823</v>
+        <v>0.2485007186454613</v>
       </c>
     </row>
     <row r="168" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23350,7 +23627,9 @@
       <c r="Y168" s="56">
         <v>26.266666666666669</v>
       </c>
-      <c r="Z168" s="56"/>
+      <c r="Z168" s="56">
+        <v>24</v>
+      </c>
       <c r="AA168" s="56"/>
       <c r="AB168" s="56"/>
       <c r="AC168" s="56"/>
@@ -23368,7 +23647,7 @@
       <c r="AO168" s="56"/>
       <c r="AP168" s="58">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ168" s="71" t="str">
         <f t="shared" si="7"/>
@@ -23457,7 +23736,9 @@
       <c r="Y169" s="56">
         <v>22.933333333333341</v>
       </c>
-      <c r="Z169" s="56"/>
+      <c r="Z169" s="56">
+        <v>21.466666666666669</v>
+      </c>
       <c r="AA169" s="56"/>
       <c r="AB169" s="56"/>
       <c r="AC169" s="56"/>
@@ -23475,19 +23756,19 @@
       <c r="AO169" s="56"/>
       <c r="AP169" s="58">
         <f t="shared" si="6"/>
-        <v>14</v>
-      </c>
-      <c r="AQ169" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ169" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>21.097777777777779</v>
       </c>
       <c r="AR169" s="71">
         <f>IFERROR(VLOOKUP(A169,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>18.928926022251918</v>
       </c>
-      <c r="AS169" s="71" t="str">
+      <c r="AS169" s="71">
         <f t="shared" si="8"/>
-        <v/>
+        <v>2.1688517555258606</v>
       </c>
     </row>
     <row r="170" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23562,7 +23843,9 @@
       <c r="Y170" s="56">
         <v>27.45</v>
       </c>
-      <c r="Z170" s="56"/>
+      <c r="Z170" s="56">
+        <v>26.3</v>
+      </c>
       <c r="AA170" s="56"/>
       <c r="AB170" s="56"/>
       <c r="AC170" s="56"/>
@@ -23580,7 +23863,7 @@
       <c r="AO170" s="56"/>
       <c r="AP170" s="58">
         <f t="shared" si="6"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ170" s="71" t="str">
         <f t="shared" si="7"/>
@@ -23671,7 +23954,9 @@
       <c r="Y171" s="56">
         <v>26.15</v>
       </c>
-      <c r="Z171" s="56"/>
+      <c r="Z171" s="56">
+        <v>25.8</v>
+      </c>
       <c r="AA171" s="56"/>
       <c r="AB171" s="56"/>
       <c r="AC171" s="56"/>
@@ -23689,11 +23974,11 @@
       <c r="AO171" s="56"/>
       <c r="AP171" s="58">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ171" s="71">
         <f t="shared" si="7"/>
-        <v>25.292222222222222</v>
+        <v>25.323958333333334</v>
       </c>
       <c r="AR171" s="71">
         <f>IFERROR(VLOOKUP(A171,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23701,7 +23986,7 @@
       </c>
       <c r="AS171" s="71">
         <f t="shared" si="8"/>
-        <v>1.2378136200716909</v>
+        <v>1.2695497311828028</v>
       </c>
     </row>
     <row r="172" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23778,7 +24063,9 @@
       <c r="Y172" s="56">
         <v>14.8</v>
       </c>
-      <c r="Z172" s="56"/>
+      <c r="Z172" s="56">
+        <v>13.66666666666667</v>
+      </c>
       <c r="AA172" s="56"/>
       <c r="AB172" s="56"/>
       <c r="AC172" s="56"/>
@@ -23796,19 +24083,19 @@
       <c r="AO172" s="56"/>
       <c r="AP172" s="58">
         <f t="shared" si="6"/>
-        <v>14</v>
-      </c>
-      <c r="AQ172" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ172" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>13.911111111111113</v>
       </c>
       <c r="AR172" s="71">
         <f>IFERROR(VLOOKUP(A172,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>12.06075185767186</v>
       </c>
-      <c r="AS172" s="71" t="str">
+      <c r="AS172" s="71">
         <f t="shared" si="8"/>
-        <v/>
+        <v>1.8503592534392528</v>
       </c>
     </row>
     <row r="173" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24429,7 +24716,9 @@
       <c r="Y179" s="56">
         <v>31.6</v>
       </c>
-      <c r="Z179" s="56"/>
+      <c r="Z179" s="56">
+        <v>32.533333333333331</v>
+      </c>
       <c r="AA179" s="56"/>
       <c r="AB179" s="56"/>
       <c r="AC179" s="56"/>
@@ -24447,11 +24736,11 @@
       <c r="AO179" s="56"/>
       <c r="AP179" s="58">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ179" s="71">
         <f t="shared" si="7"/>
-        <v>30.94222222222222</v>
+        <v>31.041666666666664</v>
       </c>
       <c r="AR179" s="71">
         <f>IFERROR(VLOOKUP(A179,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24459,7 +24748,7 @@
       </c>
       <c r="AS179" s="71">
         <f t="shared" si="8"/>
-        <v>2.4089858346524089</v>
+        <v>2.5084302790968529</v>
       </c>
     </row>
     <row r="180" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24696,7 +24985,9 @@
       <c r="Y182" s="56">
         <v>29</v>
       </c>
-      <c r="Z182" s="56"/>
+      <c r="Z182" s="56">
+        <v>28.6</v>
+      </c>
       <c r="AA182" s="56"/>
       <c r="AB182" s="56"/>
       <c r="AC182" s="56"/>
@@ -24714,11 +25005,11 @@
       <c r="AO182" s="56"/>
       <c r="AP182" s="58">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ182" s="71">
         <f t="shared" si="7"/>
-        <v>27.951111111111114</v>
+        <v>27.991666666666671</v>
       </c>
       <c r="AR182" s="71">
         <f>IFERROR(VLOOKUP(A182,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24726,7 +25017,7 @@
       </c>
       <c r="AS182" s="71">
         <f t="shared" si="8"/>
-        <v>1.3127398934941255</v>
+        <v>1.353295449049682</v>
       </c>
     </row>
     <row r="183" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24797,7 +25088,9 @@
       <c r="Y183" s="56">
         <v>29.93333333333333</v>
       </c>
-      <c r="Z183" s="56"/>
+      <c r="Z183" s="56">
+        <v>30.4</v>
+      </c>
       <c r="AA183" s="56"/>
       <c r="AB183" s="56"/>
       <c r="AC183" s="56"/>
@@ -24815,7 +25108,7 @@
       <c r="AO183" s="56"/>
       <c r="AP183" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ183" s="71" t="str">
         <f t="shared" si="7"/>
@@ -25064,7 +25357,9 @@
       <c r="Y186" s="56">
         <v>17.733333333333331</v>
       </c>
-      <c r="Z186" s="56"/>
+      <c r="Z186" s="56">
+        <v>18.666666666666671</v>
+      </c>
       <c r="AA186" s="56"/>
       <c r="AB186" s="56"/>
       <c r="AC186" s="56"/>
@@ -25082,11 +25377,11 @@
       <c r="AO186" s="56"/>
       <c r="AP186" s="58">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ186" s="71">
         <f t="shared" si="7"/>
-        <v>17.408888888888892</v>
+        <v>17.487500000000004</v>
       </c>
       <c r="AR186" s="71">
         <f>IFERROR(VLOOKUP(A186,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25094,7 +25389,7 @@
       </c>
       <c r="AS186" s="71">
         <f t="shared" si="8"/>
-        <v>1.413296899357162</v>
+        <v>1.4919080104682738</v>
       </c>
     </row>
     <row r="187" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25165,7 +25460,9 @@
       <c r="Y187" s="56">
         <v>34.06666666666667</v>
       </c>
-      <c r="Z187" s="56"/>
+      <c r="Z187" s="56">
+        <v>32.93333333333333</v>
+      </c>
       <c r="AA187" s="56"/>
       <c r="AB187" s="56"/>
       <c r="AC187" s="56"/>
@@ -25183,7 +25480,7 @@
       <c r="AO187" s="56"/>
       <c r="AP187" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ187" s="71" t="str">
         <f t="shared" si="7"/>
@@ -25274,7 +25571,9 @@
       <c r="Y188" s="56">
         <v>32.200000000000003</v>
       </c>
-      <c r="Z188" s="56"/>
+      <c r="Z188" s="56">
+        <v>32.266666666666673</v>
+      </c>
       <c r="AA188" s="56"/>
       <c r="AB188" s="56"/>
       <c r="AC188" s="56"/>
@@ -25292,11 +25591,11 @@
       <c r="AO188" s="56"/>
       <c r="AP188" s="58">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ188" s="71">
         <f t="shared" si="7"/>
-        <v>30.586666666666666</v>
+        <v>30.691666666666666</v>
       </c>
       <c r="AR188" s="71">
         <f>IFERROR(VLOOKUP(A188,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25304,7 +25603,7 @@
       </c>
       <c r="AS188" s="71">
         <f t="shared" si="8"/>
-        <v>1.6701430051841974</v>
+        <v>1.7751430051841979</v>
       </c>
     </row>
     <row r="189" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25383,7 +25682,9 @@
       <c r="Y189" s="56">
         <v>18.850000000000001</v>
       </c>
-      <c r="Z189" s="56"/>
+      <c r="Z189" s="56">
+        <v>19.05</v>
+      </c>
       <c r="AA189" s="56"/>
       <c r="AB189" s="56"/>
       <c r="AC189" s="56"/>
@@ -25401,11 +25702,11 @@
       <c r="AO189" s="56"/>
       <c r="AP189" s="58">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ189" s="71">
         <f t="shared" si="7"/>
-        <v>18.683333333333334</v>
+        <v>18.706250000000001</v>
       </c>
       <c r="AR189" s="71">
         <f>IFERROR(VLOOKUP(A189,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25413,7 +25714,7 @@
       </c>
       <c r="AS189" s="71">
         <f t="shared" si="8"/>
-        <v>1.2961143186727249</v>
+        <v>1.319030985339392</v>
       </c>
     </row>
     <row r="190" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25492,7 +25793,9 @@
       <c r="Y190" s="56">
         <v>26.666666666666671</v>
       </c>
-      <c r="Z190" s="56"/>
+      <c r="Z190" s="56">
+        <v>24.733333333333331</v>
+      </c>
       <c r="AA190" s="56"/>
       <c r="AB190" s="56"/>
       <c r="AC190" s="56"/>
@@ -25510,11 +25813,11 @@
       <c r="AO190" s="56"/>
       <c r="AP190" s="58">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ190" s="71">
         <f t="shared" si="7"/>
-        <v>26.248888888888892</v>
+        <v>26.154166666666672</v>
       </c>
       <c r="AR190" s="71">
         <f>IFERROR(VLOOKUP(A190,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25522,7 +25825,7 @@
       </c>
       <c r="AS190" s="71">
         <f t="shared" si="8"/>
-        <v>1.0043817080707207</v>
+        <v>0.90965948584850054</v>
       </c>
     </row>
     <row r="191" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25599,7 +25902,9 @@
       <c r="Y191" s="56">
         <v>28.75</v>
       </c>
-      <c r="Z191" s="56"/>
+      <c r="Z191" s="56">
+        <v>27.25</v>
+      </c>
       <c r="AA191" s="56"/>
       <c r="AB191" s="56"/>
       <c r="AC191" s="56"/>
@@ -25617,19 +25922,19 @@
       <c r="AO191" s="56"/>
       <c r="AP191" s="58">
         <f t="shared" si="6"/>
-        <v>14</v>
-      </c>
-      <c r="AQ191" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ191" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>27.079999999999995</v>
       </c>
       <c r="AR191" s="71">
         <f>IFERROR(VLOOKUP(A191,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>26.35276954000917</v>
       </c>
-      <c r="AS191" s="71" t="str">
+      <c r="AS191" s="71">
         <f t="shared" si="8"/>
-        <v/>
+        <v>0.72723045999082458</v>
       </c>
     </row>
     <row r="192" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25708,7 +26013,9 @@
       <c r="Y192" s="56">
         <v>22.2</v>
       </c>
-      <c r="Z192" s="56"/>
+      <c r="Z192" s="56">
+        <v>21.133333333333329</v>
+      </c>
       <c r="AA192" s="56"/>
       <c r="AB192" s="56"/>
       <c r="AC192" s="56"/>
@@ -25726,11 +26033,11 @@
       <c r="AO192" s="56"/>
       <c r="AP192" s="58">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ192" s="71">
         <f t="shared" si="7"/>
-        <v>21.306666666666668</v>
+        <v>21.295833333333334</v>
       </c>
       <c r="AR192" s="71">
         <f>IFERROR(VLOOKUP(A192,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25738,7 +26045,7 @@
       </c>
       <c r="AS192" s="71">
         <f t="shared" si="8"/>
-        <v>-0.30099513039176173</v>
+        <v>-0.31182846372509587</v>
       </c>
     </row>
     <row r="193" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25817,7 +26124,9 @@
       <c r="Y193" s="56">
         <v>28.86666666666666</v>
       </c>
-      <c r="Z193" s="56"/>
+      <c r="Z193" s="56">
+        <v>30.13333333333334</v>
+      </c>
       <c r="AA193" s="56"/>
       <c r="AB193" s="56"/>
       <c r="AC193" s="56"/>
@@ -25835,11 +26144,11 @@
       <c r="AO193" s="56"/>
       <c r="AP193" s="58">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ193" s="71">
         <f t="shared" si="7"/>
-        <v>27.866666666666667</v>
+        <v>28.008333333333333</v>
       </c>
       <c r="AR193" s="71">
         <f>IFERROR(VLOOKUP(A193,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25847,7 +26156,7 @@
       </c>
       <c r="AS193" s="71">
         <f t="shared" si="8"/>
-        <v>2.1791784569569081</v>
+        <v>2.3208451236235739</v>
       </c>
     </row>
     <row r="194" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25926,7 +26235,9 @@
       <c r="Y194" s="56">
         <v>22.6</v>
       </c>
-      <c r="Z194" s="56"/>
+      <c r="Z194" s="56">
+        <v>23.93333333333333</v>
+      </c>
       <c r="AA194" s="56"/>
       <c r="AB194" s="56"/>
       <c r="AC194" s="56"/>
@@ -25944,11 +26255,11 @@
       <c r="AO194" s="56"/>
       <c r="AP194" s="58">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ194" s="71">
         <f t="shared" si="7"/>
-        <v>22.426666666666669</v>
+        <v>22.520833333333336</v>
       </c>
       <c r="AR194" s="71">
         <f>IFERROR(VLOOKUP(A194,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25956,7 +26267,7 @@
       </c>
       <c r="AS194" s="71">
         <f t="shared" si="8"/>
-        <v>2.2029101951413992</v>
+        <v>2.2970768618080655</v>
       </c>
     </row>
     <row r="195" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26035,7 +26346,9 @@
       <c r="Y195" s="56">
         <v>27.13333333333334</v>
       </c>
-      <c r="Z195" s="56"/>
+      <c r="Z195" s="56">
+        <v>27.066666666666659</v>
+      </c>
       <c r="AA195" s="56"/>
       <c r="AB195" s="56"/>
       <c r="AC195" s="56"/>
@@ -26053,11 +26366,11 @@
       <c r="AO195" s="56"/>
       <c r="AP195" s="58">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ195" s="71">
         <f t="shared" si="7"/>
-        <v>25.844444444444441</v>
+        <v>25.920833333333331</v>
       </c>
       <c r="AR195" s="71">
         <f>IFERROR(VLOOKUP(A195,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26065,7 +26378,7 @@
       </c>
       <c r="AS195" s="71">
         <f t="shared" si="8"/>
-        <v>1.7170614432739129</v>
+        <v>1.7934503321628021</v>
       </c>
     </row>
     <row r="196" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26144,7 +26457,9 @@
       <c r="Y196" s="56">
         <v>22.75</v>
       </c>
-      <c r="Z196" s="56"/>
+      <c r="Z196" s="56">
+        <v>22.65</v>
+      </c>
       <c r="AA196" s="56"/>
       <c r="AB196" s="56"/>
       <c r="AC196" s="56"/>
@@ -26162,11 +26477,11 @@
       <c r="AO196" s="56"/>
       <c r="AP196" s="58">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ196" s="71">
         <f t="shared" si="7"/>
-        <v>21.706666666666663</v>
+        <v>21.765624999999996</v>
       </c>
       <c r="AR196" s="71" t="str">
         <f>IFERROR(VLOOKUP(A196,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26362,7 +26677,9 @@
       <c r="Y198" s="56">
         <v>15.15</v>
       </c>
-      <c r="Z198" s="56"/>
+      <c r="Z198" s="56">
+        <v>16</v>
+      </c>
       <c r="AA198" s="56"/>
       <c r="AB198" s="56"/>
       <c r="AC198" s="56"/>
@@ -26380,11 +26697,11 @@
       <c r="AO198" s="56"/>
       <c r="AP198" s="58">
         <f t="shared" si="9"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ198" s="71">
         <f t="shared" si="10"/>
-        <v>14.626666666666669</v>
+        <v>14.712500000000002</v>
       </c>
       <c r="AR198" s="71">
         <f>IFERROR(VLOOKUP(A198,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26392,7 +26709,7 @@
       </c>
       <c r="AS198" s="71">
         <f t="shared" si="11"/>
-        <v>1.2610541988830288</v>
+        <v>1.3468875322163623</v>
       </c>
     </row>
     <row r="199" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26471,7 +26788,9 @@
       <c r="Y199" s="56">
         <v>28.75</v>
       </c>
-      <c r="Z199" s="56"/>
+      <c r="Z199" s="56">
+        <v>29.65</v>
+      </c>
       <c r="AA199" s="56"/>
       <c r="AB199" s="56"/>
       <c r="AC199" s="56"/>
@@ -26489,11 +26808,11 @@
       <c r="AO199" s="56"/>
       <c r="AP199" s="58">
         <f t="shared" si="9"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ199" s="71">
         <f t="shared" si="10"/>
-        <v>27.143333333333331</v>
+        <v>27.299999999999997</v>
       </c>
       <c r="AR199" s="71">
         <f>IFERROR(VLOOKUP(A199,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26501,7 +26820,7 @@
       </c>
       <c r="AS199" s="71">
         <f t="shared" si="11"/>
-        <v>1.6058040650024807</v>
+        <v>1.762470731669147</v>
       </c>
     </row>
     <row r="200" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26580,7 +26899,9 @@
       <c r="Y200" s="56">
         <v>12.85</v>
       </c>
-      <c r="Z200" s="56"/>
+      <c r="Z200" s="56">
+        <v>13.15</v>
+      </c>
       <c r="AA200" s="56"/>
       <c r="AB200" s="56"/>
       <c r="AC200" s="56"/>
@@ -26598,11 +26919,11 @@
       <c r="AO200" s="56"/>
       <c r="AP200" s="58">
         <f t="shared" si="9"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ200" s="71">
         <f t="shared" si="10"/>
-        <v>13.446666666666665</v>
+        <v>13.428125</v>
       </c>
       <c r="AR200" s="71">
         <f>IFERROR(VLOOKUP(A200,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26610,7 +26931,7 @@
       </c>
       <c r="AS200" s="71">
         <f t="shared" si="11"/>
-        <v>0.64310270816274517</v>
+        <v>0.62456104149607938</v>
       </c>
     </row>
     <row r="201" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26682,8 +27003,12 @@
       <c r="X201" s="56">
         <v>14.066666666666659</v>
       </c>
-      <c r="Y201" s="56"/>
-      <c r="Z201" s="56"/>
+      <c r="Y201" s="56">
+        <v>14.53333333333333</v>
+      </c>
+      <c r="Z201" s="56">
+        <v>12.53333333333333</v>
+      </c>
       <c r="AA201" s="56"/>
       <c r="AB201" s="56"/>
       <c r="AC201" s="56"/>
@@ -26701,7 +27026,7 @@
       <c r="AO201" s="56"/>
       <c r="AP201" s="58">
         <f t="shared" si="9"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AQ201" s="71" t="str">
         <f t="shared" si="10"/>
@@ -26890,8 +27215,12 @@
       <c r="X203" s="56">
         <v>14.65</v>
       </c>
-      <c r="Y203" s="56"/>
-      <c r="Z203" s="56"/>
+      <c r="Y203" s="56">
+        <v>13.85</v>
+      </c>
+      <c r="Z203" s="56">
+        <v>14.6</v>
+      </c>
       <c r="AA203" s="56"/>
       <c r="AB203" s="56"/>
       <c r="AC203" s="56"/>
@@ -26909,19 +27238,19 @@
       <c r="AO203" s="56"/>
       <c r="AP203" s="58">
         <f t="shared" si="9"/>
-        <v>14</v>
-      </c>
-      <c r="AQ203" s="71" t="str">
+        <v>16</v>
+      </c>
+      <c r="AQ203" s="71">
         <f t="shared" si="10"/>
-        <v/>
+        <v>14.306249999999999</v>
       </c>
       <c r="AR203" s="71">
         <f>IFERROR(VLOOKUP(A203,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>13.414894116817671</v>
       </c>
-      <c r="AS203" s="71" t="str">
+      <c r="AS203" s="71">
         <f t="shared" si="11"/>
-        <v/>
+        <v>0.89135588318232806</v>
       </c>
     </row>
     <row r="204" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27097,7 +27426,9 @@
       <c r="Y205" s="56">
         <v>14.4</v>
       </c>
-      <c r="Z205" s="56"/>
+      <c r="Z205" s="56">
+        <v>14.93333333333333</v>
+      </c>
       <c r="AA205" s="56"/>
       <c r="AB205" s="56"/>
       <c r="AC205" s="56"/>
@@ -27115,7 +27446,7 @@
       <c r="AO205" s="56"/>
       <c r="AP205" s="58">
         <f t="shared" si="9"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ205" s="71" t="str">
         <f t="shared" si="10"/>
@@ -27204,7 +27535,9 @@
       <c r="Y206" s="56">
         <v>14.75</v>
       </c>
-      <c r="Z206" s="56"/>
+      <c r="Z206" s="56">
+        <v>14.85</v>
+      </c>
       <c r="AA206" s="56"/>
       <c r="AB206" s="56"/>
       <c r="AC206" s="56"/>
@@ -27222,11 +27555,11 @@
       <c r="AO206" s="56"/>
       <c r="AP206" s="58">
         <f t="shared" si="9"/>
-        <v>14</v>
-      </c>
-      <c r="AQ206" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ206" s="71">
         <f t="shared" si="10"/>
-        <v/>
+        <v>14.43</v>
       </c>
       <c r="AR206" s="71" t="str">
         <f>IFERROR(VLOOKUP(A206,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27313,7 +27646,9 @@
       <c r="Y207" s="56">
         <v>10.8</v>
       </c>
-      <c r="Z207" s="56"/>
+      <c r="Z207" s="56">
+        <v>11.3</v>
+      </c>
       <c r="AA207" s="56"/>
       <c r="AB207" s="56"/>
       <c r="AC207" s="56"/>
@@ -27331,11 +27666,11 @@
       <c r="AO207" s="56"/>
       <c r="AP207" s="58">
         <f t="shared" si="9"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ207" s="71">
         <f t="shared" si="10"/>
-        <v>10.97</v>
+        <v>10.990625000000001</v>
       </c>
       <c r="AR207" s="71" t="str">
         <f>IFERROR(VLOOKUP(A207,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27529,7 +27864,9 @@
       <c r="Y209" s="56">
         <v>8.75</v>
       </c>
-      <c r="Z209" s="56"/>
+      <c r="Z209" s="56">
+        <v>8.75</v>
+      </c>
       <c r="AA209" s="56"/>
       <c r="AB209" s="56"/>
       <c r="AC209" s="56"/>
@@ -27547,11 +27884,11 @@
       <c r="AO209" s="56"/>
       <c r="AP209" s="58">
         <f t="shared" si="9"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ209" s="71">
         <f t="shared" si="10"/>
-        <v>8.7099999999999991</v>
+        <v>8.7124999999999986</v>
       </c>
       <c r="AR209" s="71">
         <f>IFERROR(VLOOKUP(A209,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27559,7 +27896,7 @@
       </c>
       <c r="AS209" s="71">
         <f t="shared" si="11"/>
-        <v>0.62986711830959941</v>
+        <v>0.63236711830959891</v>
       </c>
     </row>
     <row r="210" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27638,7 +27975,9 @@
       <c r="Y210" s="56">
         <v>25.4</v>
       </c>
-      <c r="Z210" s="56"/>
+      <c r="Z210" s="56">
+        <v>26.15</v>
+      </c>
       <c r="AA210" s="56"/>
       <c r="AB210" s="56"/>
       <c r="AC210" s="56"/>
@@ -27656,11 +27995,11 @@
       <c r="AO210" s="56"/>
       <c r="AP210" s="58">
         <f t="shared" si="9"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ210" s="71">
         <f t="shared" si="10"/>
-        <v>25.049999999999994</v>
+        <v>25.118749999999991</v>
       </c>
       <c r="AR210" s="71" t="str">
         <f>IFERROR(VLOOKUP(A210,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
